--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00219_18600707/oocihm.N_00219_18600707.1.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00219_18600707/oocihm.N_00219_18600707.1.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -1003,7 +1003,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00219_18600707/oocihm.N_00219_18600707.1.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00219_18600707/oocihm.N_00219_18600707.1.xlsx
@@ -416,14 +416,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y103"/>
+  <dimension ref="A1:Y113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
@@ -431,7 +431,7 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
     <col width="60" customWidth="1" min="16" max="16"/>
@@ -617,16 +617,20 @@
       </c>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L32: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+00AD SOFT HYPHEN | isolated marker/symbol line :: ä¸­</t>
+          <t>L32: stray/suspicious non-ASCII glyph(s): U+4E2D CJK UNIFIED IDEOGRAPH-4E2D | isolated marker/symbol line :: 中</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L3: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢.</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]V</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]V</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L31: isolated marker/symbol line :: 9</t>
@@ -634,7 +638,7 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L5: isolated marker/symbol line :: 9</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]V</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr">
@@ -685,7 +689,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>1169</t>
+          <t>814</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr">
@@ -716,24 +720,24 @@
       </c>
       <c r="J3" s="1" t="inlineStr">
         <is>
-          <t>L80: stray/suspicious non-ASCII glyph(s): U+00AC NOT SIGN | isolated marker/symbol line :: å…¬</t>
+          <t>L43: stray/suspicious non-ASCII glyph(s): U+FF21 FULLWIDTH LATIN CAPITAL LETTER A :: SATURDAY Ａ Y</t>
         </is>
       </c>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L40: stray/suspicious non-ASCII glyph(s): U+00AC NOT SIGN :: -â‚¬And Commercial Advertiser,</t>
+          <t>L3: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •.</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
       <c r="M3" s="1" t="inlineStr"/>
       <c r="N3" s="1" t="inlineStr">
         <is>
-          <t>L32: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+00AD SOFT HYPHEN | isolated marker/symbol line :: ä¸­</t>
+          <t>L32: stray/suspicious non-ASCII glyph(s): U+4E2D CJK UNIFIED IDEOGRAPH-4E2D | isolated marker/symbol line :: 中</t>
         </is>
       </c>
       <c r="O3" s="1" t="inlineStr">
         <is>
-          <t>L117: isolated marker/symbol line :: 7</t>
+          <t>L3: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •.</t>
         </is>
       </c>
       <c r="P3" s="1" t="inlineStr">
@@ -765,7 +769,7 @@
       </c>
       <c r="W3" s="1" t="inlineStr">
         <is>
-          <t>L1126: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | abbreviation/spacing may be garbled :: N.B.As the Messrs. Pannerâ€™s engage-</t>
+          <t>L1126: abbreviation/spacing may be garbled :: N.B.As the Messrs. Panner’s engage-</t>
         </is>
       </c>
       <c r="X3" s="1" t="inlineStr"/>
@@ -807,12 +811,12 @@
       </c>
       <c r="J4" s="1" t="inlineStr">
         <is>
-          <t>L85: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L80: stray/suspicious non-ASCII glyph(s): U+516C CJK UNIFIED IDEOGRAPH-516C | isolated marker/symbol line :: 公</t>
         </is>
       </c>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>L61: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: FREDERICK STOBBS. â€” /_____</t>
+          <t>L40: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: -€And Commercial Advertiser,</t>
         </is>
       </c>
       <c r="L4" s="1" t="inlineStr"/>
@@ -824,7 +828,7 @@
       </c>
       <c r="O4" s="1" t="inlineStr">
         <is>
-          <t>L144: isolated marker/symbol line :: n</t>
+          <t>L5: isolated marker/symbol line :: 9</t>
         </is>
       </c>
       <c r="P4" s="1" t="inlineStr"/>
@@ -858,12 +862,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>194</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>84</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -886,12 +890,12 @@
       </c>
       <c r="J5" s="1" t="inlineStr">
         <is>
-          <t>L115: stray/suspicious non-ASCII glyph(s): U+00AE REGISTERED SIGN | isolated marker/symbol line :: å®¶</t>
+          <t>L85: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="K5" s="1" t="inlineStr">
         <is>
-          <t>L73: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: ountryâ€”a record, the like of which</t>
+          <t>L146: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L5" s="1" t="inlineStr"/>
@@ -903,7 +907,7 @@
       </c>
       <c r="O5" s="1" t="inlineStr">
         <is>
-          <t>L146: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L117: isolated marker/symbol line :: 7</t>
         </is>
       </c>
       <c r="P5" s="1" t="inlineStr"/>
@@ -961,12 +965,12 @@
       </c>
       <c r="J6" s="1" t="inlineStr">
         <is>
-          <t>L119: stray/suspicious non-ASCII glyph(s): U+00B4 ACUTE ACCENT | isolated marker/symbol line :: æ°´</t>
+          <t>L115: stray/suspicious non-ASCII glyph(s): U+5BB6 CJK UNIFIED IDEOGRAPH-5BB6 | isolated marker/symbol line :: 家</t>
         </is>
       </c>
       <c r="K6" s="1" t="inlineStr">
         <is>
-          <t>L92: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: e digestive organÃ© are restored to their</t>
+          <t>L208: stray/suspicious non-ASCII glyph(s): U+2022 BULLET :: ending 31st December, on such of •• said</t>
         </is>
       </c>
       <c r="L6" s="1" t="inlineStr"/>
@@ -978,13 +982,13 @@
       </c>
       <c r="O6" s="1" t="inlineStr">
         <is>
-          <t>L153: isolated marker/symbol line :: 0</t>
+          <t>L144: isolated marker/symbol line :: n</t>
         </is>
       </c>
       <c r="P6" s="1" t="inlineStr"/>
       <c r="Q6" s="1" t="inlineStr">
         <is>
-          <t>L804: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | punctuation artifact: repeated periods :: binâ€™s, Pinet, Castillonâ€™s, &amp;e..</t>
+          <t>L804: punctuation artifact: repeated periods :: bin’s, Pinet, Castillon’s, &amp;e..</t>
         </is>
       </c>
       <c r="R6" s="1" t="inlineStr"/>
@@ -1036,12 +1040,12 @@
       </c>
       <c r="J7" s="1" t="inlineStr">
         <is>
-          <t>L173: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): oMen (odd internal casing) :: "I.â€”"The oMen coming on."."</t>
+          <t>L119: stray/suspicious non-ASCII glyph(s): U+6C34 CJK UNIFIED IDEOGRAPH-6C34 | isolated marker/symbol line :: 水</t>
         </is>
       </c>
       <c r="K7" s="1" t="inlineStr">
         <is>
-          <t>L97: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: :the patientâ€™s sy stem,</t>
+          <t>L364: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L7" s="1" t="inlineStr"/>
@@ -1053,7 +1057,7 @@
       </c>
       <c r="O7" s="1" t="inlineStr">
         <is>
-          <t>L157: isolated marker/symbol line :: Â«</t>
+          <t>L146: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P7" s="1" t="inlineStr"/>
@@ -1083,7 +1087,7 @@
       </c>
       <c r="B8" s="1" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C8" s="1" t="inlineStr">
@@ -1111,12 +1115,12 @@
       </c>
       <c r="J8" s="1" t="inlineStr">
         <is>
-          <t>L198: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œ</t>
+          <t>L225: stray/suspicious non-ASCII glyph(s): U+5065 CJK UNIFIED IDEOGRAPH-5065 | isolated marker/symbol line :: 健</t>
         </is>
       </c>
       <c r="K8" s="1" t="inlineStr">
         <is>
-          <t>L114: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: wayâ€™s Pills are the best remedy</t>
+          <t>L381: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • Sold at the Manufactories of Professor</t>
         </is>
       </c>
       <c r="L8" s="1" t="inlineStr"/>
@@ -1128,7 +1132,7 @@
       </c>
       <c r="O8" s="1" t="inlineStr">
         <is>
-          <t>L170: isolated marker/symbol line :: 1</t>
+          <t>L153: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="P8" s="1" t="inlineStr"/>
@@ -1186,24 +1190,24 @@
       </c>
       <c r="J9" s="1" t="inlineStr">
         <is>
-          <t>L199: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œ</t>
+          <t>L226: stray/suspicious non-ASCII glyph(s): U+798F CJK UNIFIED IDEOGRAPH-798F | isolated marker/symbol line :: 福</t>
         </is>
       </c>
       <c r="K9" s="1" t="inlineStr">
         <is>
-          <t>L125: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: pass the housekeeperâ€™s door, and she</t>
+          <t>L388: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: •There la considerable saving by taking</t>
         </is>
       </c>
       <c r="L9" s="1" t="inlineStr"/>
       <c r="M9" s="1" t="inlineStr"/>
       <c r="N9" s="1" t="inlineStr">
         <is>
-          <t>L80: stray/suspicious non-ASCII glyph(s): U+00AC NOT SIGN | isolated marker/symbol line :: å…¬</t>
+          <t>L80: stray/suspicious non-ASCII glyph(s): U+516C CJK UNIFIED IDEOGRAPH-516C | isolated marker/symbol line :: 公</t>
         </is>
       </c>
       <c r="O9" s="1" t="inlineStr">
         <is>
-          <t>L275: isolated marker/symbol line :: C</t>
+          <t>L157: isolated marker/symbol line :: «</t>
         </is>
       </c>
       <c r="P9" s="1" t="inlineStr"/>
@@ -1211,7 +1215,7 @@
       <c r="R9" s="1" t="inlineStr"/>
       <c r="S9" s="1" t="inlineStr">
         <is>
-          <t>L421: line starts with punctuation glued to text :: ** And the wind. Lady Alice, was, meet all the ghosts in or out of Hades,</t>
+          <t>L381: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • Sold at the Manufactories of Professor</t>
         </is>
       </c>
       <c r="T9" s="1" t="inlineStr"/>
@@ -1229,12 +1233,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1257,12 +1261,12 @@
       </c>
       <c r="J10" s="1" t="inlineStr">
         <is>
-          <t>L205: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Alice.â€™ Yet I cannot tell how I shrink</t>
+          <t>L236: stray/suspicious non-ASCII glyph(s): U+9189 CJK UNIFIED IDEOGRAPH-9189 | isolated marker/symbol line :: 醉</t>
         </is>
       </c>
       <c r="K10" s="1" t="inlineStr">
         <is>
-          <t>L126: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: sleeps but lightly.â€™</t>
+          <t>L507: stray/suspicious non-ASCII glyph(s): U+2022 BULLET :: commends i self as the only relinb • prepara-</t>
         </is>
       </c>
       <c r="L10" s="1" t="inlineStr"/>
@@ -1274,7 +1278,7 @@
       </c>
       <c r="O10" s="1" t="inlineStr">
         <is>
-          <t>L277: isolated marker/symbol line :: 9</t>
+          <t>L169: isolated marker/symbol line :: ‘s</t>
         </is>
       </c>
       <c r="P10" s="1" t="inlineStr"/>
@@ -1282,7 +1286,7 @@
       <c r="R10" s="1" t="inlineStr"/>
       <c r="S10" s="1" t="inlineStr">
         <is>
-          <t>L739: line starts with punctuation glued to text :: -_choice Paintings, Sculp- tended eyes, as if they were the gates</t>
+          <t>L388: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: •There la considerable saving by taking</t>
         </is>
       </c>
       <c r="T10" s="1" t="inlineStr"/>
@@ -1305,7 +1309,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1328,24 +1332,24 @@
       </c>
       <c r="J11" s="1" t="inlineStr">
         <is>
-          <t>L225: stray/suspicious non-ASCII glyph(s): U+FFFD REPLACEMENT CHARACTER, U+00A5 YEN SIGN | isolated marker/symbol line :: å�¥</t>
+          <t>L260: stray/suspicious non-ASCII glyph(s): U+5B66 CJK UNIFIED IDEOGRAPH-5B66, U+79C1 CJK UNIFIED IDEOGRAPH-79C1, U+84C4 CJK UNIFIED IDEOGRAPH-84C4, U+9C7C CJK UNIFIED IDEOGRAPH-9C7C :: 学 私 蓄 鱼</t>
         </is>
       </c>
       <c r="K11" s="1" t="inlineStr">
         <is>
-          <t>L128: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: "Are we near the housekeeperâ€™s</t>
+          <t>L703: stray/suspicious non-ASCII glyph(s): U+25A0 BLACK SQUARE :: system subject to ■ return of the disease—</t>
         </is>
       </c>
       <c r="L11" s="1" t="inlineStr"/>
       <c r="M11" s="1" t="inlineStr"/>
       <c r="N11" s="1" t="inlineStr">
         <is>
-          <t>L85: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L85: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="O11" s="1" t="inlineStr">
         <is>
-          <t>L364: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L170: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="P11" s="1" t="inlineStr"/>
@@ -1353,7 +1357,7 @@
       <c r="R11" s="1" t="inlineStr"/>
       <c r="S11" s="1" t="inlineStr">
         <is>
-          <t>L1053: line starts with digit/letter garbage token | suspicious token(s): 1Office (letter/digit mix) :: 1Office Department, recently eloped</t>
+          <t>L421: line starts with punctuation glued to text :: ** And the wind. Lady Alice, was, meet all the ghosts in or out of Hades,</t>
         </is>
       </c>
       <c r="T11" s="1" t="inlineStr"/>
@@ -1371,12 +1375,12 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>112</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>31</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
@@ -1399,12 +1403,12 @@
       </c>
       <c r="J12" s="1" t="inlineStr">
         <is>
-          <t>L226: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: ç¦�</t>
+          <t>L261: stray/suspicious non-ASCII glyph(s): U+624B CJK UNIFIED IDEOGRAPH-624B, U+6559 CJK UNIFIED IDEOGRAPH-6559, U+85CF CJK UNIFIED IDEOGRAPH-85CF :: 手 教 藏</t>
         </is>
       </c>
       <c r="K12" s="1" t="inlineStr">
         <is>
-          <t>L132: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: They would sayâ€”-It is only Lady</t>
+          <t>L753: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • either the walls of the parlor, library, or of mine, so wide open that I could see the</t>
         </is>
       </c>
       <c r="L12" s="1" t="inlineStr"/>
@@ -1416,7 +1420,7 @@
       </c>
       <c r="O12" s="1" t="inlineStr">
         <is>
-          <t>L398: isolated marker/symbol line :: I</t>
+          <t>L275: isolated marker/symbol line :: C</t>
         </is>
       </c>
       <c r="P12" s="1" t="inlineStr"/>
@@ -1424,7 +1428,7 @@
       <c r="R12" s="1" t="inlineStr"/>
       <c r="S12" s="1" t="inlineStr">
         <is>
-          <t>L1080: line starts with digit/letter garbage token | suspicious token(s): 1sun (letter/digit mix) :: 1sun who will give information which will</t>
+          <t>L739: line starts with punctuation glued to text :: -_choice Paintings, Sculp- tended eyes, as if they were the gates</t>
         </is>
       </c>
       <c r="T12" s="1" t="inlineStr"/>
@@ -1470,12 +1474,12 @@
       </c>
       <c r="J13" s="1" t="inlineStr">
         <is>
-          <t>L260: stray/suspicious non-ASCII glyph(s): U+00AD SOFT HYPHEN, U+00A6 BROKEN BAR, U+FFFD REPLACEMENT CHARACTER, U+00B1 PLUS-MINUS SIGN :: å­¦ ç§� è“„ é±¼</t>
+          <t>L286: stray/suspicious non-ASCII glyph(s): U+4E00 CJK UNIFIED IDEOGRAPH-4E00 :: Irg 一 7.</t>
         </is>
       </c>
       <c r="K13" s="1" t="inlineStr">
         <is>
-          <t>L133: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Alice.â€™ Yet I cannot tell how I shrink</t>
+          <t>L939: stray/suspicious non-ASCII glyph(s): U+25A0 BLACK SQUARE :: ■ January, 1860, at which time the books will</t>
         </is>
       </c>
       <c r="L13" s="1" t="inlineStr"/>
@@ -1487,13 +1491,17 @@
       </c>
       <c r="O13" s="1" t="inlineStr">
         <is>
-          <t>L402: isolated marker/symbol line :: C</t>
+          <t>L277: isolated marker/symbol line :: 9</t>
         </is>
       </c>
       <c r="P13" s="1" t="inlineStr"/>
       <c r="Q13" s="1" t="inlineStr"/>
       <c r="R13" s="1" t="inlineStr"/>
-      <c r="S13" s="1" t="inlineStr"/>
+      <c r="S13" s="1" t="inlineStr">
+        <is>
+          <t>L753: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • either the walls of the parlor, library, or of mine, so wide open that I could see the</t>
+        </is>
+      </c>
       <c r="T13" s="1" t="inlineStr"/>
       <c r="U13" s="1" t="inlineStr"/>
       <c r="V13" s="1" t="inlineStr"/>
@@ -1514,14 +1522,14 @@
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr"/>
       <c r="E14" s="1" t="inlineStr"/>
       <c r="F14" s="1" t="inlineStr">
         <is>
-          <t>L971: candidate OCR token mismatch vs other OCR: "Eyspepsia" vs "Dyspepsia" :: for Eyspepsia. Being al-</t>
+          <t>L831: suspicious token(s): ChAndon's (odd internal casing) | candidate OCR token mismatch vs other OCR: "Moet" vs "Meet" :: CHAMPAGNES-Moet &amp; ChAndon's, and</t>
         </is>
       </c>
       <c r="G14" s="1" t="inlineStr"/>
@@ -1537,30 +1545,34 @@
       </c>
       <c r="J14" s="1" t="inlineStr">
         <is>
-          <t>L261: stray/suspicious non-ASCII glyph(s): U+2022 BULLET, U+2122 TRADE MARK SIGN, U+FFFD REPLACEMENT CHARACTER :: æ‰‹ æ•™ è—�</t>
+          <t>L734: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | isolated marker/symbol line :: ©</t>
         </is>
       </c>
       <c r="K14" s="1" t="inlineStr">
         <is>
-          <t>L134: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: from being seen by them. Noâ€”I will</t>
+          <t>L1156: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L14" s="1" t="inlineStr"/>
       <c r="M14" s="1" t="inlineStr"/>
       <c r="N14" s="1" t="inlineStr">
         <is>
-          <t>L115: stray/suspicious non-ASCII glyph(s): U+00AE REGISTERED SIGN | isolated marker/symbol line :: å®¶</t>
+          <t>L115: stray/suspicious non-ASCII glyph(s): U+5BB6 CJK UNIFIED IDEOGRAPH-5BB6 | isolated marker/symbol line :: 家</t>
         </is>
       </c>
       <c r="O14" s="1" t="inlineStr">
         <is>
-          <t>L724: isolated marker/symbol line :: 00</t>
+          <t>L364: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P14" s="1" t="inlineStr"/>
       <c r="Q14" s="1" t="inlineStr"/>
       <c r="R14" s="1" t="inlineStr"/>
-      <c r="S14" s="1" t="inlineStr"/>
+      <c r="S14" s="1" t="inlineStr">
+        <is>
+          <t>L1053: line starts with digit/letter garbage token | suspicious token(s): 1Office (letter/digit mix) :: 1Office Department, recently eloped</t>
+        </is>
+      </c>
       <c r="T14" s="1" t="inlineStr"/>
       <c r="U14" s="1" t="inlineStr"/>
       <c r="V14" s="1" t="inlineStr"/>
@@ -1588,7 +1600,7 @@
       <c r="E15" s="1" t="inlineStr"/>
       <c r="F15" s="1" t="inlineStr">
         <is>
-          <t>L1141: candidate OCR token mismatch vs other OCR: "havo" vs "have" :: " There is; but we should havo to with her riding-master.</t>
+          <t>L971: candidate OCR token mismatch vs other OCR: "Eyspepsia" vs "Dyspepsia" :: for Eyspepsia. Being al-</t>
         </is>
       </c>
       <c r="G15" s="1" t="inlineStr"/>
@@ -1604,14 +1616,10 @@
       </c>
       <c r="J15" s="1" t="inlineStr">
         <is>
-          <t>L286: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+20AC EURO SIGN :: Irg ä¸€ 7.</t>
-        </is>
-      </c>
-      <c r="K15" s="1" t="inlineStr">
-        <is>
-          <t>L146: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
+          <t>L735: stray/suspicious non-ASCII glyph(s): U+5FC3 CJK UNIFIED IDEOGRAPH-5FC3 | isolated marker/symbol line :: 心</t>
+        </is>
+      </c>
+      <c r="K15" s="1" t="inlineStr"/>
       <c r="L15" s="1" t="inlineStr"/>
       <c r="M15" s="1" t="inlineStr"/>
       <c r="N15" s="1" t="inlineStr">
@@ -1621,13 +1629,17 @@
       </c>
       <c r="O15" s="1" t="inlineStr">
         <is>
-          <t>L840: isolated marker/symbol line :: *</t>
+          <t>L398: isolated marker/symbol line :: I</t>
         </is>
       </c>
       <c r="P15" s="1" t="inlineStr"/>
       <c r="Q15" s="1" t="inlineStr"/>
       <c r="R15" s="1" t="inlineStr"/>
-      <c r="S15" s="1" t="inlineStr"/>
+      <c r="S15" s="1" t="inlineStr">
+        <is>
+          <t>L1080: line starts with digit/letter garbage token | suspicious token(s): 1sun (letter/digit mix) :: 1sun who will give information which will</t>
+        </is>
+      </c>
       <c r="T15" s="1" t="inlineStr"/>
       <c r="U15" s="1" t="inlineStr"/>
       <c r="V15" s="1" t="inlineStr"/>
@@ -1653,7 +1665,11 @@
       </c>
       <c r="D16" s="1" t="inlineStr"/>
       <c r="E16" s="1" t="inlineStr"/>
-      <c r="F16" s="1" t="inlineStr"/>
+      <c r="F16" s="1" t="inlineStr">
+        <is>
+          <t>L1141: candidate OCR token mismatch vs other OCR: "havo" vs "have" :: " There is; but we should havo to with her riding-master.</t>
+        </is>
+      </c>
       <c r="G16" s="1" t="inlineStr"/>
       <c r="H16" s="1" t="inlineStr">
         <is>
@@ -1667,14 +1683,10 @@
       </c>
       <c r="J16" s="1" t="inlineStr">
         <is>
-          <t>L330: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Streets.â€” Near the Post Office.</t>
-        </is>
-      </c>
-      <c r="K16" s="1" t="inlineStr">
-        <is>
-          <t>L169: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE :: â€˜s</t>
-        </is>
-      </c>
+          <t>L777: stray/suspicious non-ASCII glyph(s): U+4E5F CJK UNIFIED IDEOGRAPH-4E5F | isolated marker/symbol line :: 也</t>
+        </is>
+      </c>
+      <c r="K16" s="1" t="inlineStr"/>
       <c r="L16" s="1" t="inlineStr"/>
       <c r="M16" s="1" t="inlineStr"/>
       <c r="N16" s="1" t="inlineStr">
@@ -1684,7 +1696,7 @@
       </c>
       <c r="O16" s="1" t="inlineStr">
         <is>
-          <t>L1031: isolated marker/symbol line :: ^1</t>
+          <t>L402: isolated marker/symbol line :: C</t>
         </is>
       </c>
       <c r="P16" s="1" t="inlineStr"/>
@@ -1730,14 +1742,10 @@
       </c>
       <c r="J17" s="1" t="inlineStr">
         <is>
-          <t>L418: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: rh Ã¦ a. Dysen'ery. Griping in the Bowels</t>
-        </is>
-      </c>
-      <c r="K17" s="1" t="inlineStr">
-        <is>
-          <t>L181: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: PACAUDâ€™S NEW Bl</t>
-        </is>
-      </c>
+          <t>L835: stray/suspicious non-ASCII glyph(s): U+4E00 CJK UNIFIED IDEOGRAPH-4E00 :: ALSO, 一</t>
+        </is>
+      </c>
+      <c r="K17" s="1" t="inlineStr"/>
       <c r="L17" s="1" t="inlineStr"/>
       <c r="M17" s="1" t="inlineStr"/>
       <c r="N17" s="1" t="inlineStr">
@@ -1747,7 +1755,7 @@
       </c>
       <c r="O17" s="1" t="inlineStr">
         <is>
-          <t>L1092: isolated marker/symbol line :: M</t>
+          <t>L724: isolated marker/symbol line :: 00</t>
         </is>
       </c>
       <c r="P17" s="1" t="inlineStr"/>
@@ -1771,7 +1779,7 @@
       <c r="G18" s="1" t="inlineStr"/>
       <c r="H18" s="1" t="inlineStr">
         <is>
-          <t>L173: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): oMen (odd internal casing) :: "I.â€”"The oMen coming on."."</t>
+          <t>L173: suspicious token(s): oMen (odd internal casing) :: "I.—"The oMen coming on."."</t>
         </is>
       </c>
       <c r="I18" s="1" t="inlineStr">
@@ -1781,24 +1789,20 @@
       </c>
       <c r="J18" s="1" t="inlineStr">
         <is>
-          <t>L522: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: ã€�</t>
-        </is>
-      </c>
-      <c r="K18" s="1" t="inlineStr">
-        <is>
-          <t>L208: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: ending 31st December, on such of â€¢â€¢ said</t>
-        </is>
-      </c>
+          <t>L935: stray/suspicious non-ASCII glyph(s): U+6C99 CJK UNIFIED IDEOGRAPH-6C99 | isolated marker/symbol line :: 沙</t>
+        </is>
+      </c>
+      <c r="K18" s="1" t="inlineStr"/>
       <c r="L18" s="1" t="inlineStr"/>
       <c r="M18" s="1" t="inlineStr"/>
       <c r="N18" s="1" t="inlineStr">
         <is>
-          <t>L119: stray/suspicious non-ASCII glyph(s): U+00B4 ACUTE ACCENT | isolated marker/symbol line :: æ°´</t>
+          <t>L119: stray/suspicious non-ASCII glyph(s): U+6C34 CJK UNIFIED IDEOGRAPH-6C34 | isolated marker/symbol line :: 水</t>
         </is>
       </c>
       <c r="O18" s="1" t="inlineStr">
         <is>
-          <t>L1100: isolated marker/symbol line :: a</t>
+          <t>L840: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="P18" s="1" t="inlineStr"/>
@@ -1832,14 +1836,10 @@
       </c>
       <c r="J19" s="1" t="inlineStr">
         <is>
-          <t>L565: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: "Then, with a curling lipâ€”â€”</t>
-        </is>
-      </c>
-      <c r="K19" s="1" t="inlineStr">
-        <is>
-          <t>L235: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: N. Dâ€”The Certificates of the Shares in the</t>
-        </is>
-      </c>
+          <t>L936: stray/suspicious non-ASCII glyph(s): U+5C81 CJK UNIFIED IDEOGRAPH-5C81 | isolated marker/symbol line :: 岁</t>
+        </is>
+      </c>
+      <c r="K19" s="1" t="inlineStr"/>
       <c r="L19" s="1" t="inlineStr"/>
       <c r="M19" s="1" t="inlineStr"/>
       <c r="N19" s="1" t="inlineStr">
@@ -1849,7 +1849,7 @@
       </c>
       <c r="O19" s="1" t="inlineStr">
         <is>
-          <t>L1102: isolated marker/symbol line :: 99</t>
+          <t>L1031: isolated marker/symbol line :: ^1</t>
         </is>
       </c>
       <c r="P19" s="1" t="inlineStr"/>
@@ -1883,14 +1883,10 @@
       </c>
       <c r="J20" s="1" t="inlineStr">
         <is>
-          <t>L616: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œI</t>
-        </is>
-      </c>
-      <c r="K20" s="1" t="inlineStr">
-        <is>
-          <t>L244: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: â€” pany of Canada,â€� as decided at a General</t>
-        </is>
-      </c>
+          <t>L947: stray/suspicious non-ASCII glyph(s): U+5FC3 CJK UNIFIED IDEOGRAPH-5FC3 | isolated marker/symbol line :: 心</t>
+        </is>
+      </c>
+      <c r="K20" s="1" t="inlineStr"/>
       <c r="L20" s="1" t="inlineStr"/>
       <c r="M20" s="1" t="inlineStr"/>
       <c r="N20" s="1" t="inlineStr">
@@ -1900,7 +1896,7 @@
       </c>
       <c r="O20" s="1" t="inlineStr">
         <is>
-          <t>L1107: isolated marker/symbol line :: 8</t>
+          <t>L1092: isolated marker/symbol line :: M</t>
         </is>
       </c>
       <c r="P20" s="1" t="inlineStr"/>
@@ -1929,19 +1925,15 @@
       </c>
       <c r="I21" s="1" t="inlineStr">
         <is>
-          <t>L735: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): 54a (letter/digit mix) :: to the Galleries. 54a, Broadway, New York not â€ž</t>
+          <t>L735: suspicious token(s): 54a (letter/digit mix) :: to the Galleries. 54a, Broadway, New York not „</t>
         </is>
       </c>
       <c r="J21" s="1" t="inlineStr">
         <is>
-          <t>L620: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: did. And I hear it now â€” l hear it</t>
-        </is>
-      </c>
-      <c r="K21" s="1" t="inlineStr">
-        <is>
-          <t>L271: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: - "How did I come here?â€� headâ€”</t>
-        </is>
-      </c>
+          <t>L948: stray/suspicious non-ASCII glyph(s): U+5FC3 CJK UNIFIED IDEOGRAPH-5FC3 | isolated marker/symbol line :: 心</t>
+        </is>
+      </c>
+      <c r="K21" s="1" t="inlineStr"/>
       <c r="L21" s="1" t="inlineStr"/>
       <c r="M21" s="1" t="inlineStr"/>
       <c r="N21" s="1" t="inlineStr">
@@ -1951,7 +1943,7 @@
       </c>
       <c r="O21" s="1" t="inlineStr">
         <is>
-          <t>L1116: isolated marker/symbol line :: a</t>
+          <t>L1100: isolated marker/symbol line :: a</t>
         </is>
       </c>
       <c r="P21" s="1" t="inlineStr"/>
@@ -1985,14 +1977,10 @@
       </c>
       <c r="J22" s="1" t="inlineStr">
         <is>
-          <t>L630: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: head â€”</t>
-        </is>
-      </c>
-      <c r="K22" s="1" t="inlineStr">
-        <is>
-          <t>L273: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: -â€œ I carried you.â€� â€œ Ah, yes! I am right at last; this</t>
-        </is>
-      </c>
+          <t>L961: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
+        </is>
+      </c>
+      <c r="K22" s="1" t="inlineStr"/>
       <c r="L22" s="1" t="inlineStr"/>
       <c r="M22" s="1" t="inlineStr"/>
       <c r="N22" s="1" t="inlineStr">
@@ -2002,7 +1990,7 @@
       </c>
       <c r="O22" s="1" t="inlineStr">
         <is>
-          <t>L1136: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: â€”</t>
+          <t>L1102: isolated marker/symbol line :: 99</t>
         </is>
       </c>
       <c r="P22" s="1" t="inlineStr"/>
@@ -2036,14 +2024,10 @@
       </c>
       <c r="J23" s="1" t="inlineStr">
         <is>
-          <t>L645: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: to forsake it never, never r moreâ€”the</t>
-        </is>
-      </c>
-      <c r="K23" s="1" t="inlineStr">
-        <is>
-          <t>L281: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: ST. NORBERT Dâ€™ARTHABASKA,</t>
-        </is>
-      </c>
+          <t>L1125: stray/suspicious non-ASCII glyph(s): U+821E CJK UNIFIED IDEOGRAPH-821E, U+6167 CJK UNIFIED IDEOGRAPH-6167 :: 舞 慧</t>
+        </is>
+      </c>
+      <c r="K23" s="1" t="inlineStr"/>
       <c r="L23" s="1" t="inlineStr"/>
       <c r="M23" s="1" t="inlineStr"/>
       <c r="N23" s="1" t="inlineStr">
@@ -2053,7 +2037,7 @@
       </c>
       <c r="O23" s="1" t="inlineStr">
         <is>
-          <t>L1138: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: â€”</t>
+          <t>L1107: isolated marker/symbol line :: 8</t>
         </is>
       </c>
       <c r="P23" s="1" t="inlineStr"/>
@@ -2087,14 +2071,10 @@
       </c>
       <c r="J24" s="1" t="inlineStr">
         <is>
-          <t>L654: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: that I might take it back; adding â€”" I</t>
-        </is>
-      </c>
-      <c r="K24" s="1" t="inlineStr">
-        <is>
-          <t>L298: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: " Then, with a curling lipâ€” is the haunted room: I know my way</t>
-        </is>
-      </c>
+          <t>L1126: stray/suspicious non-ASCII glyph(s): U+75C5 CJK UNIFIED IDEOGRAPH-75C5 | isolated marker/symbol line :: 病</t>
+        </is>
+      </c>
+      <c r="K24" s="1" t="inlineStr"/>
       <c r="L24" s="1" t="inlineStr"/>
       <c r="M24" s="1" t="inlineStr"/>
       <c r="N24" s="1" t="inlineStr">
@@ -2104,7 +2084,7 @@
       </c>
       <c r="O24" s="1" t="inlineStr">
         <is>
-          <t>L1146: isolated marker/symbol line :: -</t>
+          <t>L1116: isolated marker/symbol line :: a</t>
         </is>
       </c>
       <c r="P24" s="1" t="inlineStr"/>
@@ -2136,16 +2116,8 @@
           <t>L954: suspicious token(s): CommissionAgent (odd internal casing) :: CommissionAgent,</t>
         </is>
       </c>
-      <c r="J25" s="1" t="inlineStr">
-        <is>
-          <t>L680: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: dicale:â€” A poor woman at Verneuil</t>
-        </is>
-      </c>
-      <c r="K25" s="1" t="inlineStr">
-        <is>
-          <t>L300: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: " Where did you find me, pray ?" now.â€�</t>
-        </is>
-      </c>
+      <c r="J25" s="1" t="inlineStr"/>
+      <c r="K25" s="1" t="inlineStr"/>
       <c r="L25" s="1" t="inlineStr"/>
       <c r="M25" s="1" t="inlineStr"/>
       <c r="N25" s="1" t="inlineStr">
@@ -2155,7 +2127,7 @@
       </c>
       <c r="O25" s="1" t="inlineStr">
         <is>
-          <t>L1148: isolated marker/symbol line :: 1</t>
+          <t>L1136: isolated marker/symbol line :: —</t>
         </is>
       </c>
       <c r="P25" s="1" t="inlineStr"/>
@@ -2187,16 +2159,8 @@
           <t>L1016: suspicious token(s): ICommission (odd internal casing) :: ICommission Agent.</t>
         </is>
       </c>
-      <c r="J26" s="1" t="inlineStr">
-        <is>
-          <t>L697: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): DrspnPata (odd internal casing) :: DrspnPata â€” No person with thie distres.</t>
-        </is>
-      </c>
-      <c r="K26" s="1" t="inlineStr">
-        <is>
-          <t>L307: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: to go to it.â€� Ity and mustiness, I could not tell. Lit-</t>
-        </is>
-      </c>
+      <c r="J26" s="1" t="inlineStr"/>
+      <c r="K26" s="1" t="inlineStr"/>
       <c r="L26" s="1" t="inlineStr"/>
       <c r="M26" s="1" t="inlineStr"/>
       <c r="N26" s="1" t="inlineStr">
@@ -2206,7 +2170,7 @@
       </c>
       <c r="O26" s="1" t="inlineStr">
         <is>
-          <t>L1152: isolated marker/symbol line :: &amp;</t>
+          <t>L1138: isolated marker/symbol line :: —</t>
         </is>
       </c>
       <c r="P26" s="1" t="inlineStr"/>
@@ -2238,26 +2202,18 @@
           <t>L1024: suspicious token(s): S3 (letter/digit mix) :: stead of S3, in order to defray extra postage,</t>
         </is>
       </c>
-      <c r="J27" s="1" t="inlineStr">
-        <is>
-          <t>L700: stray/suspicious non-ASCII glyph(s): U+00A4 CURRENCY SIGN :: Erysipelas, FlÃ¤ulung., Four snd Agm. For</t>
-        </is>
-      </c>
-      <c r="K27" s="1" t="inlineStr">
-        <is>
-          <t>L309: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: " Tis impossible. I see. Your the did I think then what memoriesâ€”</t>
-        </is>
-      </c>
+      <c r="J27" s="1" t="inlineStr"/>
+      <c r="K27" s="1" t="inlineStr"/>
       <c r="L27" s="1" t="inlineStr"/>
       <c r="M27" s="1" t="inlineStr"/>
       <c r="N27" s="1" t="inlineStr">
         <is>
-          <t>L221: isolated marker/symbol line :: 0</t>
+          <t>L198: isolated marker/symbol line :: “</t>
         </is>
       </c>
       <c r="O27" s="1" t="inlineStr">
         <is>
-          <t>L1154: isolated marker/symbol line :: #</t>
+          <t>L1146: isolated marker/symbol line :: -</t>
         </is>
       </c>
       <c r="P27" s="1" t="inlineStr"/>
@@ -2289,26 +2245,18 @@
           <t>L1048: suspicious token(s): inNew (odd internal casing) :: the heaviest ship-owners inNew Eng-</t>
         </is>
       </c>
-      <c r="J28" s="1" t="inlineStr">
-        <is>
-          <t>L707: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): MEaCuRal (odd internal casing) :: MEaCuRal Diseases.â€” Xerer falls to era-</t>
-        </is>
-      </c>
-      <c r="K28" s="1" t="inlineStr">
-        <is>
-          <t>L314: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: reviving, she went on through berâ€”would ere long find their being and</t>
-        </is>
-      </c>
+      <c r="J28" s="1" t="inlineStr"/>
+      <c r="K28" s="1" t="inlineStr"/>
       <c r="L28" s="1" t="inlineStr"/>
       <c r="M28" s="1" t="inlineStr"/>
       <c r="N28" s="1" t="inlineStr">
         <is>
-          <t>L223: isolated marker/symbol line :: B</t>
+          <t>L199: isolated marker/symbol line :: “</t>
         </is>
       </c>
       <c r="O28" s="1" t="inlineStr">
         <is>
-          <t>L1156: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L1148: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="P28" s="1" t="inlineStr"/>
@@ -2340,26 +2288,18 @@
           <t>L1053: line starts with digit/letter garbage token | suspicious token(s): 1Office (letter/digit mix) :: 1Office Department, recently eloped</t>
         </is>
       </c>
-      <c r="J29" s="1" t="inlineStr">
-        <is>
-          <t>L734: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | isolated marker/symbol line :: Â©</t>
-        </is>
-      </c>
-      <c r="K29" s="1" t="inlineStr">
-        <is>
-          <t>L364: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
+      <c r="J29" s="1" t="inlineStr"/>
+      <c r="K29" s="1" t="inlineStr"/>
       <c r="L29" s="1" t="inlineStr"/>
       <c r="M29" s="1" t="inlineStr"/>
       <c r="N29" s="1" t="inlineStr">
         <is>
-          <t>L225: stray/suspicious non-ASCII glyph(s): U+FFFD REPLACEMENT CHARACTER, U+00A5 YEN SIGN | isolated marker/symbol line :: å�¥</t>
+          <t>L221: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O29" s="1" t="inlineStr">
         <is>
-          <t>L1158: isolated marker/symbol line :: 1</t>
+          <t>L1152: isolated marker/symbol line :: &amp;</t>
         </is>
       </c>
       <c r="P29" s="1" t="inlineStr"/>
@@ -2391,24 +2331,20 @@
           <t>L1080: line starts with digit/letter garbage token | suspicious token(s): 1sun (letter/digit mix) :: 1sun who will give information which will</t>
         </is>
       </c>
-      <c r="J30" s="1" t="inlineStr">
-        <is>
-          <t>L818: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: RUMSâ€”Fine old old London Dock Jamaica and</t>
-        </is>
-      </c>
-      <c r="K30" s="1" t="inlineStr">
-        <is>
-          <t>L369: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: CAUTION â€”None are genome unless</t>
-        </is>
-      </c>
+      <c r="J30" s="1" t="inlineStr"/>
+      <c r="K30" s="1" t="inlineStr"/>
       <c r="L30" s="1" t="inlineStr"/>
       <c r="M30" s="1" t="inlineStr"/>
       <c r="N30" s="1" t="inlineStr">
         <is>
-          <t>L226: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: ç¦�</t>
-        </is>
-      </c>
-      <c r="O30" s="1" t="inlineStr"/>
+          <t>L223: isolated marker/symbol line :: B</t>
+        </is>
+      </c>
+      <c r="O30" s="1" t="inlineStr">
+        <is>
+          <t>L1154: isolated marker/symbol line :: #</t>
+        </is>
+      </c>
       <c r="P30" s="1" t="inlineStr"/>
       <c r="Q30" s="1" t="inlineStr"/>
       <c r="R30" s="1" t="inlineStr"/>
@@ -2438,24 +2374,20 @@
           <t>L1104: suspicious token(s): applicatioMENRY (odd internal casing) :: applicatioMENRY CHAPMAN</t>
         </is>
       </c>
-      <c r="J31" s="1" t="inlineStr">
-        <is>
-          <t>L835: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+20AC EURO SIGN :: ALSO, ä¸€</t>
-        </is>
-      </c>
-      <c r="K31" s="1" t="inlineStr">
-        <is>
-          <t>L381: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ Sold at the Manufactories of Professor</t>
-        </is>
-      </c>
+      <c r="J31" s="1" t="inlineStr"/>
+      <c r="K31" s="1" t="inlineStr"/>
       <c r="L31" s="1" t="inlineStr"/>
       <c r="M31" s="1" t="inlineStr"/>
       <c r="N31" s="1" t="inlineStr">
         <is>
-          <t>L227: isolated marker/symbol line :: -</t>
-        </is>
-      </c>
-      <c r="O31" s="1" t="inlineStr"/>
+          <t>L225: stray/suspicious non-ASCII glyph(s): U+5065 CJK UNIFIED IDEOGRAPH-5065 | isolated marker/symbol line :: 健</t>
+        </is>
+      </c>
+      <c r="O31" s="1" t="inlineStr">
+        <is>
+          <t>L1156: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
+        </is>
+      </c>
       <c r="P31" s="1" t="inlineStr"/>
       <c r="Q31" s="1" t="inlineStr"/>
       <c r="R31" s="1" t="inlineStr"/>
@@ -2481,24 +2413,20 @@
         </is>
       </c>
       <c r="I32" s="1" t="inlineStr"/>
-      <c r="J32" s="1" t="inlineStr">
-        <is>
-          <t>L909: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 225 â€œ0</t>
-        </is>
-      </c>
-      <c r="K32" s="1" t="inlineStr">
-        <is>
-          <t>L388: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢There la considerable saving by taking</t>
-        </is>
-      </c>
+      <c r="J32" s="1" t="inlineStr"/>
+      <c r="K32" s="1" t="inlineStr"/>
       <c r="L32" s="1" t="inlineStr"/>
       <c r="M32" s="1" t="inlineStr"/>
       <c r="N32" s="1" t="inlineStr">
         <is>
-          <t>L236: isolated marker/symbol line :: é†‰</t>
-        </is>
-      </c>
-      <c r="O32" s="1" t="inlineStr"/>
+          <t>L226: stray/suspicious non-ASCII glyph(s): U+798F CJK UNIFIED IDEOGRAPH-798F | isolated marker/symbol line :: 福</t>
+        </is>
+      </c>
+      <c r="O32" s="1" t="inlineStr">
+        <is>
+          <t>L1158: isolated marker/symbol line :: 1</t>
+        </is>
+      </c>
       <c r="P32" s="1" t="inlineStr"/>
       <c r="Q32" s="1" t="inlineStr"/>
       <c r="R32" s="1" t="inlineStr"/>
@@ -2524,21 +2452,13 @@
         </is>
       </c>
       <c r="I33" s="1" t="inlineStr"/>
-      <c r="J33" s="1" t="inlineStr">
-        <is>
-          <t>L935: stray/suspicious non-ASCII glyph(s): U+2122 TRADE MARK SIGN :: æ²™</t>
-        </is>
-      </c>
-      <c r="K33" s="1" t="inlineStr">
-        <is>
-          <t>L406: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: " Why did you not leave me where to forsake it never, never moreâ€”the</t>
-        </is>
-      </c>
+      <c r="J33" s="1" t="inlineStr"/>
+      <c r="K33" s="1" t="inlineStr"/>
       <c r="L33" s="1" t="inlineStr"/>
       <c r="M33" s="1" t="inlineStr"/>
       <c r="N33" s="1" t="inlineStr">
         <is>
-          <t>L242: isolated marker/symbol line :: 1</t>
+          <t>L227: isolated marker/symbol line :: -</t>
         </is>
       </c>
       <c r="O33" s="1" t="inlineStr"/>
@@ -2567,21 +2487,13 @@
         </is>
       </c>
       <c r="I34" s="1" t="inlineStr"/>
-      <c r="J34" s="1" t="inlineStr">
-        <is>
-          <t>L936: stray/suspicious non-ASCII glyph(s): U+FFFD REPLACEMENT CHARACTER :: å²�</t>
-        </is>
-      </c>
-      <c r="K34" s="1" t="inlineStr">
-        <is>
-          <t>L415: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: terrible moon might have distorted that I might take it back; addingâ€”"I</t>
-        </is>
-      </c>
+      <c r="J34" s="1" t="inlineStr"/>
+      <c r="K34" s="1" t="inlineStr"/>
       <c r="L34" s="1" t="inlineStr"/>
       <c r="M34" s="1" t="inlineStr"/>
       <c r="N34" s="1" t="inlineStr">
         <is>
-          <t>L275: isolated marker/symbol line :: b</t>
+          <t>L236: stray/suspicious non-ASCII glyph(s): U+9189 CJK UNIFIED IDEOGRAPH-9189 | isolated marker/symbol line :: 醉</t>
         </is>
       </c>
       <c r="O34" s="1" t="inlineStr"/>
@@ -2610,21 +2522,13 @@
         </is>
       </c>
       <c r="I35" s="1" t="inlineStr"/>
-      <c r="J35" s="1" t="inlineStr">
-        <is>
-          <t>L961: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
-        </is>
-      </c>
-      <c r="K35" s="1" t="inlineStr">
-        <is>
-          <t>L485: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: DR. EATONâ€™S</t>
-        </is>
-      </c>
+      <c r="J35" s="1" t="inlineStr"/>
+      <c r="K35" s="1" t="inlineStr"/>
       <c r="L35" s="1" t="inlineStr"/>
       <c r="M35" s="1" t="inlineStr"/>
       <c r="N35" s="1" t="inlineStr">
         <is>
-          <t>L289: isolated marker/symbol line :: .</t>
+          <t>L242: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O35" s="1" t="inlineStr"/>
@@ -2649,25 +2553,17 @@
       <c r="G36" s="1" t="inlineStr"/>
       <c r="H36" s="1" t="inlineStr">
         <is>
-          <t>L697: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): DrspnPata (odd internal casing) :: DrspnPata â€” No person with thie distres.</t>
+          <t>L697: suspicious token(s): DrspnPata (odd internal casing) :: DrspnPata — No person with thie distres.</t>
         </is>
       </c>
       <c r="I36" s="1" t="inlineStr"/>
-      <c r="J36" s="1" t="inlineStr">
-        <is>
-          <t>L1000: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: Shakespeare and his Friends.â€� Second: A</t>
-        </is>
-      </c>
-      <c r="K36" s="1" t="inlineStr">
-        <is>
-          <t>L507: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: commends i self as the only relinb â€¢ prepara-</t>
-        </is>
-      </c>
+      <c r="J36" s="1" t="inlineStr"/>
+      <c r="K36" s="1" t="inlineStr"/>
       <c r="L36" s="1" t="inlineStr"/>
       <c r="M36" s="1" t="inlineStr"/>
       <c r="N36" s="1" t="inlineStr">
         <is>
-          <t>L290: isolated marker/symbol line :: .</t>
+          <t>L275: isolated marker/symbol line :: b</t>
         </is>
       </c>
       <c r="O36" s="1" t="inlineStr"/>
@@ -2692,25 +2588,17 @@
       <c r="G37" s="1" t="inlineStr"/>
       <c r="H37" s="1" t="inlineStr">
         <is>
-          <t>L707: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): MEaCuRal (odd internal casing) :: MEaCuRal Diseases.â€” Xerer falls to era-</t>
+          <t>L707: suspicious token(s): MEaCuRal (odd internal casing) :: MEaCuRal Diseases.— Xerer falls to era-</t>
         </is>
       </c>
       <c r="I37" s="1" t="inlineStr"/>
-      <c r="J37" s="1" t="inlineStr">
-        <is>
-          <t>L1082: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œHow is this? Why do you take</t>
-        </is>
-      </c>
-      <c r="K37" s="1" t="inlineStr">
-        <is>
-          <t>L513: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: relieving pain, it has no equalâ€”being an anti</t>
-        </is>
-      </c>
+      <c r="J37" s="1" t="inlineStr"/>
+      <c r="K37" s="1" t="inlineStr"/>
       <c r="L37" s="1" t="inlineStr"/>
       <c r="M37" s="1" t="inlineStr"/>
       <c r="N37" s="1" t="inlineStr">
         <is>
-          <t>L335: isolated marker/symbol line :: H</t>
+          <t>L289: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O37" s="1" t="inlineStr"/>
@@ -2740,16 +2628,12 @@
       </c>
       <c r="I38" s="1" t="inlineStr"/>
       <c r="J38" s="1" t="inlineStr"/>
-      <c r="K38" s="1" t="inlineStr">
-        <is>
-          <t>L521: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: take n ne but Dr. Estonâ€™s INFANTI E COR-</t>
-        </is>
-      </c>
+      <c r="K38" s="1" t="inlineStr"/>
       <c r="L38" s="1" t="inlineStr"/>
       <c r="M38" s="1" t="inlineStr"/>
       <c r="N38" s="1" t="inlineStr">
         <is>
-          <t>L341: isolated marker/symbol line :: ~</t>
+          <t>L290: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O38" s="1" t="inlineStr"/>
@@ -2779,16 +2663,12 @@
       </c>
       <c r="I39" s="1" t="inlineStr"/>
       <c r="J39" s="1" t="inlineStr"/>
-      <c r="K39" s="1" t="inlineStr">
-        <is>
-          <t>L541: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Streets.â€”Near the Post Office.</t>
-        </is>
-      </c>
+      <c r="K39" s="1" t="inlineStr"/>
       <c r="L39" s="1" t="inlineStr"/>
       <c r="M39" s="1" t="inlineStr"/>
       <c r="N39" s="1" t="inlineStr">
         <is>
-          <t>L364: isolated marker/symbol line :: 4</t>
+          <t>L335: isolated marker/symbol line :: H</t>
         </is>
       </c>
       <c r="O39" s="1" t="inlineStr"/>
@@ -2818,16 +2698,12 @@
       </c>
       <c r="I40" s="1" t="inlineStr"/>
       <c r="J40" s="1" t="inlineStr"/>
-      <c r="K40" s="1" t="inlineStr">
-        <is>
-          <t>L584: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: did. And I hear it nowâ€”I hear it markable cure ofa case</t>
-        </is>
-      </c>
+      <c r="K40" s="1" t="inlineStr"/>
       <c r="L40" s="1" t="inlineStr"/>
       <c r="M40" s="1" t="inlineStr"/>
       <c r="N40" s="1" t="inlineStr">
         <is>
-          <t>L401: isolated marker/symbol line :: 78</t>
+          <t>L341: isolated marker/symbol line :: ~</t>
         </is>
       </c>
       <c r="O40" s="1" t="inlineStr"/>
@@ -2857,16 +2733,12 @@
       </c>
       <c r="I41" s="1" t="inlineStr"/>
       <c r="J41" s="1" t="inlineStr"/>
-      <c r="K41" s="1" t="inlineStr">
-        <is>
-          <t>L598: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: FFATâ€™S</t>
-        </is>
-      </c>
+      <c r="K41" s="1" t="inlineStr"/>
       <c r="L41" s="1" t="inlineStr"/>
       <c r="M41" s="1" t="inlineStr"/>
       <c r="N41" s="1" t="inlineStr">
         <is>
-          <t>L442: isolated marker/symbol line :: 4</t>
+          <t>L364: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O41" s="1" t="inlineStr"/>
@@ -2896,16 +2768,12 @@
       </c>
       <c r="I42" s="1" t="inlineStr"/>
       <c r="J42" s="1" t="inlineStr"/>
-      <c r="K42" s="1" t="inlineStr">
-        <is>
-          <t>L636: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: FENDTâ€™S</t>
-        </is>
-      </c>
+      <c r="K42" s="1" t="inlineStr"/>
       <c r="L42" s="1" t="inlineStr"/>
       <c r="M42" s="1" t="inlineStr"/>
       <c r="N42" s="1" t="inlineStr">
         <is>
-          <t>L451: isolated marker/symbol line :: 4</t>
+          <t>L401: isolated marker/symbol line :: 78</t>
         </is>
       </c>
       <c r="O42" s="1" t="inlineStr"/>
@@ -2935,16 +2803,12 @@
       </c>
       <c r="I43" s="1" t="inlineStr"/>
       <c r="J43" s="1" t="inlineStr"/>
-      <c r="K43" s="1" t="inlineStr">
-        <is>
-          <t>L664: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: LADIESâ€™ UNDERCLOTHING,</t>
-        </is>
-      </c>
+      <c r="K43" s="1" t="inlineStr"/>
       <c r="L43" s="1" t="inlineStr"/>
       <c r="M43" s="1" t="inlineStr"/>
       <c r="N43" s="1" t="inlineStr">
         <is>
-          <t>L453: isolated marker/symbol line :: 000</t>
+          <t>L442: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O43" s="1" t="inlineStr"/>
@@ -2974,16 +2838,12 @@
       </c>
       <c r="I44" s="1" t="inlineStr"/>
       <c r="J44" s="1" t="inlineStr"/>
-      <c r="K44" s="1" t="inlineStr">
-        <is>
-          <t>L669: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Ladiesâ€™ MORNING &amp; BREAKFAST</t>
-        </is>
-      </c>
+      <c r="K44" s="1" t="inlineStr"/>
       <c r="L44" s="1" t="inlineStr"/>
       <c r="M44" s="1" t="inlineStr"/>
       <c r="N44" s="1" t="inlineStr">
         <is>
-          <t>L454: isolated marker/symbol line :: V</t>
+          <t>L451: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O44" s="1" t="inlineStr"/>
@@ -3013,16 +2873,12 @@
       </c>
       <c r="I45" s="1" t="inlineStr"/>
       <c r="J45" s="1" t="inlineStr"/>
-      <c r="K45" s="1" t="inlineStr">
-        <is>
-          <t>L676: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 211 and 23 Notre Dame â€” al</t>
-        </is>
-      </c>
+      <c r="K45" s="1" t="inlineStr"/>
       <c r="L45" s="1" t="inlineStr"/>
       <c r="M45" s="1" t="inlineStr"/>
       <c r="N45" s="1" t="inlineStr">
         <is>
-          <t>L455: isolated marker/symbol line :: 4</t>
+          <t>L453: isolated marker/symbol line :: 000</t>
         </is>
       </c>
       <c r="O45" s="1" t="inlineStr"/>
@@ -3052,16 +2908,12 @@
       </c>
       <c r="I46" s="1" t="inlineStr"/>
       <c r="J46" s="1" t="inlineStr"/>
-      <c r="K46" s="1" t="inlineStr">
-        <is>
-          <t>L690: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Complaints â€”In the south and west, where</t>
-        </is>
-      </c>
+      <c r="K46" s="1" t="inlineStr"/>
       <c r="L46" s="1" t="inlineStr"/>
       <c r="M46" s="1" t="inlineStr"/>
       <c r="N46" s="1" t="inlineStr">
         <is>
-          <t>L456: isolated marker/symbol line :: 6</t>
+          <t>L454: isolated marker/symbol line :: V</t>
         </is>
       </c>
       <c r="O46" s="1" t="inlineStr"/>
@@ -3086,21 +2938,17 @@
       <c r="G47" s="1" t="inlineStr"/>
       <c r="H47" s="1" t="inlineStr">
         <is>
-          <t>L831: suspicious token(s): ChAndon's (odd internal casing) :: CHAMPAGNES-Moet &amp; ChAndon's, and</t>
+          <t>L831: suspicious token(s): ChAndon's (odd internal casing) | candidate OCR token mismatch vs other OCR: "Moet" vs "Meet" :: CHAMPAGNES-Moet &amp; ChAndon's, and</t>
         </is>
       </c>
       <c r="I47" s="1" t="inlineStr"/>
       <c r="J47" s="1" t="inlineStr"/>
-      <c r="K47" s="1" t="inlineStr">
-        <is>
-          <t>L696: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: DYSPEPSIA â€”No person with this distres-</t>
-        </is>
-      </c>
+      <c r="K47" s="1" t="inlineStr"/>
       <c r="L47" s="1" t="inlineStr"/>
       <c r="M47" s="1" t="inlineStr"/>
       <c r="N47" s="1" t="inlineStr">
         <is>
-          <t>L457: isolated marker/symbol line :: 1</t>
+          <t>L455: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O47" s="1" t="inlineStr"/>
@@ -3130,16 +2978,12 @@
       </c>
       <c r="I48" s="1" t="inlineStr"/>
       <c r="J48" s="1" t="inlineStr"/>
-      <c r="K48" s="1" t="inlineStr">
-        <is>
-          <t>L703: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: system subject to â– return of the diseaseâ€”</t>
-        </is>
-      </c>
+      <c r="K48" s="1" t="inlineStr"/>
       <c r="L48" s="1" t="inlineStr"/>
       <c r="M48" s="1" t="inlineStr"/>
       <c r="N48" s="1" t="inlineStr">
         <is>
-          <t>L458: isolated marker/symbol line :: B</t>
+          <t>L456: isolated marker/symbol line :: 6</t>
         </is>
       </c>
       <c r="O48" s="1" t="inlineStr"/>
@@ -3169,16 +3013,12 @@
       </c>
       <c r="I49" s="1" t="inlineStr"/>
       <c r="J49" s="1" t="inlineStr"/>
-      <c r="K49" s="1" t="inlineStr">
-        <is>
-          <t>L704: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: a cure by these medicines to permanent. â€”</t>
-        </is>
-      </c>
+      <c r="K49" s="1" t="inlineStr"/>
       <c r="L49" s="1" t="inlineStr"/>
       <c r="M49" s="1" t="inlineStr"/>
       <c r="N49" s="1" t="inlineStr">
         <is>
-          <t>L464: isolated marker/symbol line :: p</t>
+          <t>L457: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O49" s="1" t="inlineStr"/>
@@ -3208,16 +3048,12 @@
       </c>
       <c r="I50" s="1" t="inlineStr"/>
       <c r="J50" s="1" t="inlineStr"/>
-      <c r="K50" s="1" t="inlineStr">
-        <is>
-          <t>L709: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Lockjaw.â€”The following very re-</t>
-        </is>
-      </c>
+      <c r="K50" s="1" t="inlineStr"/>
       <c r="L50" s="1" t="inlineStr"/>
       <c r="M50" s="1" t="inlineStr"/>
       <c r="N50" s="1" t="inlineStr">
         <is>
-          <t>L474: isolated marker/symbol line :: 0</t>
+          <t>L458: isolated marker/symbol line :: B</t>
         </is>
       </c>
       <c r="O50" s="1" t="inlineStr"/>
@@ -3247,16 +3083,12 @@
       </c>
       <c r="I51" s="1" t="inlineStr"/>
       <c r="J51" s="1" t="inlineStr"/>
-      <c r="K51" s="1" t="inlineStr">
-        <is>
-          <t>L726: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: The angry glow faded from her face, dicaleâ€”A poor woman at Verneuil</t>
-        </is>
-      </c>
+      <c r="K51" s="1" t="inlineStr"/>
       <c r="L51" s="1" t="inlineStr"/>
       <c r="M51" s="1" t="inlineStr"/>
       <c r="N51" s="1" t="inlineStr">
         <is>
-          <t>L506: isolated marker/symbol line :: 1</t>
+          <t>L464: isolated marker/symbol line :: p</t>
         </is>
       </c>
       <c r="O51" s="1" t="inlineStr"/>
@@ -3286,16 +3118,12 @@
       </c>
       <c r="I52" s="1" t="inlineStr"/>
       <c r="J52" s="1" t="inlineStr"/>
-      <c r="K52" s="1" t="inlineStr">
-        <is>
-          <t>L733: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: One Year. Third - A fire. Season Admission her, and rising from the couch. â€œI do!</t>
-        </is>
-      </c>
+      <c r="K52" s="1" t="inlineStr"/>
       <c r="L52" s="1" t="inlineStr"/>
       <c r="M52" s="1" t="inlineStr"/>
       <c r="N52" s="1" t="inlineStr">
         <is>
-          <t>L510: isolated marker/symbol line :: F</t>
+          <t>L474: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O52" s="1" t="inlineStr"/>
@@ -3325,16 +3153,12 @@
       </c>
       <c r="I53" s="1" t="inlineStr"/>
       <c r="J53" s="1" t="inlineStr"/>
-      <c r="K53" s="1" t="inlineStr">
-        <is>
-          <t>L735: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): 54a (letter/digit mix) :: to the Galleries. 54a, Broadway, New York not â€ž</t>
-        </is>
-      </c>
+      <c r="K53" s="1" t="inlineStr"/>
       <c r="L53" s="1" t="inlineStr"/>
       <c r="M53" s="1" t="inlineStr"/>
       <c r="N53" s="1" t="inlineStr">
         <is>
-          <t>L511: isolated marker/symbol line :: 0</t>
+          <t>L506: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O53" s="1" t="inlineStr"/>
@@ -3364,16 +3188,12 @@
       </c>
       <c r="I54" s="1" t="inlineStr"/>
       <c r="J54" s="1" t="inlineStr"/>
-      <c r="K54" s="1" t="inlineStr">
-        <is>
-          <t>L742: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: and Foreign Artists. | â€œ I do not hear it,â€� she said, after a</t>
-        </is>
-      </c>
+      <c r="K54" s="1" t="inlineStr"/>
       <c r="L54" s="1" t="inlineStr"/>
       <c r="M54" s="1" t="inlineStr"/>
       <c r="N54" s="1" t="inlineStr">
         <is>
-          <t>L515: isolated marker/symbol line :: 2</t>
+          <t>L510: isolated marker/symbol line :: F</t>
         </is>
       </c>
       <c r="O54" s="1" t="inlineStr"/>
@@ -3403,16 +3223,12 @@
       </c>
       <c r="I55" s="1" t="inlineStr"/>
       <c r="J55" s="1" t="inlineStr"/>
-      <c r="K55" s="1" t="inlineStr">
-        <is>
-          <t>L744: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: The beautiful Engraving, Which every Sub- â€žit must be now.â€� Then</t>
-        </is>
-      </c>
+      <c r="K55" s="1" t="inlineStr"/>
       <c r="L55" s="1" t="inlineStr"/>
       <c r="M55" s="1" t="inlineStr"/>
       <c r="N55" s="1" t="inlineStr">
         <is>
-          <t>L522: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: ã€�</t>
+          <t>L511: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O55" s="1" t="inlineStr"/>
@@ -3442,16 +3258,12 @@
       </c>
       <c r="I56" s="1" t="inlineStr"/>
       <c r="J56" s="1" t="inlineStr"/>
-      <c r="K56" s="1" t="inlineStr">
-        <is>
-          <t>L746: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: 4. Shakspeare and his Friends,â€� turning towards me. she laid her hand</t>
-        </is>
-      </c>
+      <c r="K56" s="1" t="inlineStr"/>
       <c r="L56" s="1" t="inlineStr"/>
       <c r="M56" s="1" t="inlineStr"/>
       <c r="N56" s="1" t="inlineStr">
         <is>
-          <t>L536: isolated marker/symbol line :: 4</t>
+          <t>L515: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O56" s="1" t="inlineStr"/>
@@ -3481,16 +3293,12 @@
       </c>
       <c r="I57" s="1" t="inlineStr"/>
       <c r="J57" s="1" t="inlineStr"/>
-      <c r="K57" s="1" t="inlineStr">
-        <is>
-          <t>L753: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ either the walls of the parlor, library, or of mine, so wide open that I could see the</t>
-        </is>
-      </c>
+      <c r="K57" s="1" t="inlineStr"/>
       <c r="L57" s="1" t="inlineStr"/>
       <c r="M57" s="1" t="inlineStr"/>
       <c r="N57" s="1" t="inlineStr">
         <is>
-          <t>L545: isolated marker/symbol line :: S</t>
+          <t>L522: isolated marker/symbol line :: 、</t>
         </is>
       </c>
       <c r="O57" s="1" t="inlineStr"/>
@@ -3520,16 +3328,12 @@
       </c>
       <c r="I58" s="1" t="inlineStr"/>
       <c r="J58" s="1" t="inlineStr"/>
-      <c r="K58" s="1" t="inlineStr">
-        <is>
-          <t>L785: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: J HOWARD MARCH &amp; CO.â€™s MADEI-</t>
-        </is>
-      </c>
+      <c r="K58" s="1" t="inlineStr"/>
       <c r="L58" s="1" t="inlineStr"/>
       <c r="M58" s="1" t="inlineStr"/>
       <c r="N58" s="1" t="inlineStr">
         <is>
-          <t>L546: isolated marker/symbol line :: 2</t>
+          <t>L536: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O58" s="1" t="inlineStr"/>
@@ -3555,16 +3359,12 @@
       <c r="H59" s="1" t="inlineStr"/>
       <c r="I59" s="1" t="inlineStr"/>
       <c r="J59" s="1" t="inlineStr"/>
-      <c r="K59" s="1" t="inlineStr">
-        <is>
-          <t>L789: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: JUL S ROBIN &amp; CO.â€™S COGNAC BRAN-</t>
-        </is>
-      </c>
+      <c r="K59" s="1" t="inlineStr"/>
       <c r="L59" s="1" t="inlineStr"/>
       <c r="M59" s="1" t="inlineStr"/>
       <c r="N59" s="1" t="inlineStr">
         <is>
-          <t>L592: isolated marker/symbol line :: 9</t>
+          <t>L545: isolated marker/symbol line :: S</t>
         </is>
       </c>
       <c r="O59" s="1" t="inlineStr"/>
@@ -3590,16 +3390,12 @@
       <c r="H60" s="1" t="inlineStr"/>
       <c r="I60" s="1" t="inlineStr"/>
       <c r="J60" s="1" t="inlineStr"/>
-      <c r="K60" s="1" t="inlineStr">
-        <is>
-          <t>L792: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: OFFLEY. CE AMP &amp; co.â€™s PORT WIN S</t>
-        </is>
-      </c>
+      <c r="K60" s="1" t="inlineStr"/>
       <c r="L60" s="1" t="inlineStr"/>
       <c r="M60" s="1" t="inlineStr"/>
       <c r="N60" s="1" t="inlineStr">
         <is>
-          <t>L594: isolated marker/symbol line :: 4</t>
+          <t>L546: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O60" s="1" t="inlineStr"/>
@@ -3625,16 +3421,12 @@
       <c r="H61" s="1" t="inlineStr"/>
       <c r="I61" s="1" t="inlineStr"/>
       <c r="J61" s="1" t="inlineStr"/>
-      <c r="K61" s="1" t="inlineStr">
-        <is>
-          <t>L794: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: WM YOUNGER &amp; CO.â€™S EDINBURGH</t>
-        </is>
-      </c>
+      <c r="K61" s="1" t="inlineStr"/>
       <c r="L61" s="1" t="inlineStr"/>
       <c r="M61" s="1" t="inlineStr"/>
       <c r="N61" s="1" t="inlineStr">
         <is>
-          <t>L603: isolated marker/symbol line :: 7</t>
+          <t>L592: isolated marker/symbol line :: 9</t>
         </is>
       </c>
       <c r="O61" s="1" t="inlineStr"/>
@@ -3660,16 +3452,12 @@
       <c r="H62" s="1" t="inlineStr"/>
       <c r="I62" s="1" t="inlineStr"/>
       <c r="J62" s="1" t="inlineStr"/>
-      <c r="K62" s="1" t="inlineStr">
-        <is>
-          <t>L802: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: for sale on very advantageous terms:â€”</t>
-        </is>
-      </c>
+      <c r="K62" s="1" t="inlineStr"/>
       <c r="L62" s="1" t="inlineStr"/>
       <c r="M62" s="1" t="inlineStr"/>
       <c r="N62" s="1" t="inlineStr">
         <is>
-          <t>L622: isolated marker/symbol line :: 4</t>
+          <t>L594: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O62" s="1" t="inlineStr"/>
@@ -3695,16 +3483,12 @@
       <c r="H63" s="1" t="inlineStr"/>
       <c r="I63" s="1" t="inlineStr"/>
       <c r="J63" s="1" t="inlineStr"/>
-      <c r="K63" s="1" t="inlineStr">
-        <is>
-          <t>L803: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: BRANDIES-Martellâ€™s, Hennesseyâ€™s, Ro-</t>
-        </is>
-      </c>
+      <c r="K63" s="1" t="inlineStr"/>
       <c r="L63" s="1" t="inlineStr"/>
       <c r="M63" s="1" t="inlineStr"/>
       <c r="N63" s="1" t="inlineStr">
         <is>
-          <t>L685: isolated marker/symbol line :: 0</t>
+          <t>L603: isolated marker/symbol line :: 7</t>
         </is>
       </c>
       <c r="O63" s="1" t="inlineStr"/>
@@ -3730,16 +3514,12 @@
       <c r="H64" s="1" t="inlineStr"/>
       <c r="I64" s="1" t="inlineStr"/>
       <c r="J64" s="1" t="inlineStr"/>
-      <c r="K64" s="1" t="inlineStr">
-        <is>
-          <t>L804: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | punctuation artifact: repeated periods :: binâ€™s, Pinet, Castillonâ€™s, &amp;e..</t>
-        </is>
-      </c>
+      <c r="K64" s="1" t="inlineStr"/>
       <c r="L64" s="1" t="inlineStr"/>
       <c r="M64" s="1" t="inlineStr"/>
       <c r="N64" s="1" t="inlineStr">
         <is>
-          <t>L686: isolated marker/symbol line :: 18</t>
+          <t>L616: isolated marker/symbol line :: “I</t>
         </is>
       </c>
       <c r="O64" s="1" t="inlineStr"/>
@@ -3765,16 +3545,12 @@
       <c r="H65" s="1" t="inlineStr"/>
       <c r="I65" s="1" t="inlineStr"/>
       <c r="J65" s="1" t="inlineStr"/>
-      <c r="K65" s="1" t="inlineStr">
-        <is>
-          <t>L806: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: GINSâ€”Holland and English, of best brands</t>
-        </is>
-      </c>
+      <c r="K65" s="1" t="inlineStr"/>
       <c r="L65" s="1" t="inlineStr"/>
       <c r="M65" s="1" t="inlineStr"/>
       <c r="N65" s="1" t="inlineStr">
         <is>
-          <t>L687: isolated marker/symbol line :: 1</t>
+          <t>L622: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O65" s="1" t="inlineStr"/>
@@ -3800,16 +3576,12 @@
       <c r="H66" s="1" t="inlineStr"/>
       <c r="I66" s="1" t="inlineStr"/>
       <c r="J66" s="1" t="inlineStr"/>
-      <c r="K66" s="1" t="inlineStr">
-        <is>
-          <t>L812: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: ALES Bassâ€™, Allsoppâ€™s and Youngerâ€™s, in</t>
-        </is>
-      </c>
+      <c r="K66" s="1" t="inlineStr"/>
       <c r="L66" s="1" t="inlineStr"/>
       <c r="M66" s="1" t="inlineStr"/>
       <c r="N66" s="1" t="inlineStr">
         <is>
-          <t>L710: isolated marker/symbol line :: 8</t>
+          <t>L685: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O66" s="1" t="inlineStr"/>
@@ -3835,16 +3607,12 @@
       <c r="H67" s="1" t="inlineStr"/>
       <c r="I67" s="1" t="inlineStr"/>
       <c r="J67" s="1" t="inlineStr"/>
-      <c r="K67" s="1" t="inlineStr">
-        <is>
-          <t>L815: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: PORTERSâ€”Bridgeâ€™s, Hibbertâ€™s, and Guin-</t>
-        </is>
-      </c>
+      <c r="K67" s="1" t="inlineStr"/>
       <c r="L67" s="1" t="inlineStr"/>
       <c r="M67" s="1" t="inlineStr"/>
       <c r="N67" s="1" t="inlineStr">
         <is>
-          <t>L734: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | isolated marker/symbol line :: Â©</t>
+          <t>L686: isolated marker/symbol line :: 18</t>
         </is>
       </c>
       <c r="O67" s="1" t="inlineStr"/>
@@ -3870,16 +3638,12 @@
       <c r="H68" s="1" t="inlineStr"/>
       <c r="I68" s="1" t="inlineStr"/>
       <c r="J68" s="1" t="inlineStr"/>
-      <c r="K68" s="1" t="inlineStr">
-        <is>
-          <t>L816: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: nessâ€™, in wood and bottle</t>
-        </is>
-      </c>
+      <c r="K68" s="1" t="inlineStr"/>
       <c r="L68" s="1" t="inlineStr"/>
       <c r="M68" s="1" t="inlineStr"/>
       <c r="N68" s="1" t="inlineStr">
         <is>
-          <t>L744: isolated marker/symbol line :: 103</t>
+          <t>L687: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O68" s="1" t="inlineStr"/>
@@ -3905,16 +3669,12 @@
       <c r="H69" s="1" t="inlineStr"/>
       <c r="I69" s="1" t="inlineStr"/>
       <c r="J69" s="1" t="inlineStr"/>
-      <c r="K69" s="1" t="inlineStr">
-        <is>
-          <t>L818: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: WHISKIESâ€”SCOTCH and IRISH, of the</t>
-        </is>
-      </c>
+      <c r="K69" s="1" t="inlineStr"/>
       <c r="L69" s="1" t="inlineStr"/>
       <c r="M69" s="1" t="inlineStr"/>
       <c r="N69" s="1" t="inlineStr">
         <is>
-          <t>L762: isolated marker/symbol line :: F</t>
+          <t>L710: isolated marker/symbol line :: 8</t>
         </is>
       </c>
       <c r="O69" s="1" t="inlineStr"/>
@@ -3940,16 +3700,12 @@
       <c r="H70" s="1" t="inlineStr"/>
       <c r="I70" s="1" t="inlineStr"/>
       <c r="J70" s="1" t="inlineStr"/>
-      <c r="K70" s="1" t="inlineStr">
-        <is>
-          <t>L822: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE :: PORT WINESâ€”Offley &amp; Co â€˜s. Spademan a</t>
-        </is>
-      </c>
+      <c r="K70" s="1" t="inlineStr"/>
       <c r="L70" s="1" t="inlineStr"/>
       <c r="M70" s="1" t="inlineStr"/>
       <c r="N70" s="1" t="inlineStr">
         <is>
-          <t>L778: isolated marker/symbol line :: 6</t>
+          <t>L734: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | isolated marker/symbol line :: ©</t>
         </is>
       </c>
       <c r="O70" s="1" t="inlineStr"/>
@@ -3975,16 +3731,12 @@
       <c r="H71" s="1" t="inlineStr"/>
       <c r="I71" s="1" t="inlineStr"/>
       <c r="J71" s="1" t="inlineStr"/>
-      <c r="K71" s="1" t="inlineStr">
-        <is>
-          <t>L825: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: SHERRIESâ€” Crump. Suter &amp; Co.â€™s, Do</t>
-        </is>
-      </c>
+      <c r="K71" s="1" t="inlineStr"/>
       <c r="L71" s="1" t="inlineStr"/>
       <c r="M71" s="1" t="inlineStr"/>
       <c r="N71" s="1" t="inlineStr">
         <is>
-          <t>L820: isolated marker/symbol line :: 7</t>
+          <t>L735: stray/suspicious non-ASCII glyph(s): U+5FC3 CJK UNIFIED IDEOGRAPH-5FC3 | isolated marker/symbol line :: 心</t>
         </is>
       </c>
       <c r="O71" s="1" t="inlineStr"/>
@@ -4010,16 +3762,12 @@
       <c r="H72" s="1" t="inlineStr"/>
       <c r="I72" s="1" t="inlineStr"/>
       <c r="J72" s="1" t="inlineStr"/>
-      <c r="K72" s="1" t="inlineStr">
-        <is>
-          <t>L826: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE, U+2122 TRADE MARK SIGN :: meeq.â€˜s, Pemartinâ€™s &amp;c.</t>
-        </is>
-      </c>
+      <c r="K72" s="1" t="inlineStr"/>
       <c r="L72" s="1" t="inlineStr"/>
       <c r="M72" s="1" t="inlineStr"/>
       <c r="N72" s="1" t="inlineStr">
         <is>
-          <t>L842: isolated marker/symbol line :: 8</t>
+          <t>L744: isolated marker/symbol line :: 103</t>
         </is>
       </c>
       <c r="O72" s="1" t="inlineStr"/>
@@ -4045,16 +3793,12 @@
       <c r="H73" s="1" t="inlineStr"/>
       <c r="I73" s="1" t="inlineStr"/>
       <c r="J73" s="1" t="inlineStr"/>
-      <c r="K73" s="1" t="inlineStr">
-        <is>
-          <t>L828: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: CHAMPAGNESâ€”Meet &amp; Chandonâ€™s, and</t>
-        </is>
-      </c>
+      <c r="K73" s="1" t="inlineStr"/>
       <c r="L73" s="1" t="inlineStr"/>
       <c r="M73" s="1" t="inlineStr"/>
       <c r="N73" s="1" t="inlineStr">
         <is>
-          <t>L844: isolated marker/symbol line :: V</t>
+          <t>L762: isolated marker/symbol line :: F</t>
         </is>
       </c>
       <c r="O73" s="1" t="inlineStr"/>
@@ -4080,16 +3824,12 @@
       <c r="H74" s="1" t="inlineStr"/>
       <c r="I74" s="1" t="inlineStr"/>
       <c r="J74" s="1" t="inlineStr"/>
-      <c r="K74" s="1" t="inlineStr">
-        <is>
-          <t>L831: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: CLARETSâ€”Of various ages, in wood and</t>
-        </is>
-      </c>
+      <c r="K74" s="1" t="inlineStr"/>
       <c r="L74" s="1" t="inlineStr"/>
       <c r="M74" s="1" t="inlineStr"/>
       <c r="N74" s="1" t="inlineStr">
         <is>
-          <t>L846: isolated marker/symbol line :: 55</t>
+          <t>L777: stray/suspicious non-ASCII glyph(s): U+4E5F CJK UNIFIED IDEOGRAPH-4E5F | isolated marker/symbol line :: 也</t>
         </is>
       </c>
       <c r="O74" s="1" t="inlineStr"/>
@@ -4115,16 +3855,12 @@
       <c r="H75" s="1" t="inlineStr"/>
       <c r="I75" s="1" t="inlineStr"/>
       <c r="J75" s="1" t="inlineStr"/>
-      <c r="K75" s="1" t="inlineStr">
-        <is>
-          <t>L848: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: No. I Gibâ€™d Arichat,</t>
-        </is>
-      </c>
+      <c r="K75" s="1" t="inlineStr"/>
       <c r="L75" s="1" t="inlineStr"/>
       <c r="M75" s="1" t="inlineStr"/>
       <c r="N75" s="1" t="inlineStr">
         <is>
-          <t>L848: isolated marker/symbol line :: 7</t>
+          <t>L778: isolated marker/symbol line :: 6</t>
         </is>
       </c>
       <c r="O75" s="1" t="inlineStr"/>
@@ -4150,16 +3886,12 @@
       <c r="H76" s="1" t="inlineStr"/>
       <c r="I76" s="1" t="inlineStr"/>
       <c r="J76" s="1" t="inlineStr"/>
-      <c r="K76" s="1" t="inlineStr">
-        <is>
-          <t>L874: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: MERCURAL DISEASES â€”Never fails to era-</t>
-        </is>
-      </c>
+      <c r="K76" s="1" t="inlineStr"/>
       <c r="L76" s="1" t="inlineStr"/>
       <c r="M76" s="1" t="inlineStr"/>
       <c r="N76" s="1" t="inlineStr">
         <is>
-          <t>L883: isolated marker/symbol line :: C</t>
+          <t>L820: isolated marker/symbol line :: 7</t>
         </is>
       </c>
       <c r="O76" s="1" t="inlineStr"/>
@@ -4185,16 +3917,12 @@
       <c r="H77" s="1" t="inlineStr"/>
       <c r="I77" s="1" t="inlineStr"/>
       <c r="J77" s="1" t="inlineStr"/>
-      <c r="K77" s="1" t="inlineStr">
-        <is>
-          <t>L881: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Palpitation of the Heart, Painterâ€™s Cholic.</t>
-        </is>
-      </c>
+      <c r="K77" s="1" t="inlineStr"/>
       <c r="L77" s="1" t="inlineStr"/>
       <c r="M77" s="1" t="inlineStr"/>
       <c r="N77" s="1" t="inlineStr">
         <is>
-          <t>L892: isolated marker/symbol line :: M</t>
+          <t>L842: isolated marker/symbol line :: 8</t>
         </is>
       </c>
       <c r="O77" s="1" t="inlineStr"/>
@@ -4220,16 +3948,12 @@
       <c r="H78" s="1" t="inlineStr"/>
       <c r="I78" s="1" t="inlineStr"/>
       <c r="J78" s="1" t="inlineStr"/>
-      <c r="K78" s="1" t="inlineStr">
-        <is>
-          <t>L883: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: I'll ES â€”The original Proprietor of these</t>
-        </is>
-      </c>
+      <c r="K78" s="1" t="inlineStr"/>
       <c r="L78" s="1" t="inlineStr"/>
       <c r="M78" s="1" t="inlineStr"/>
       <c r="N78" s="1" t="inlineStr">
         <is>
-          <t>L905: symbol-only separator/garbage line :: 1960.</t>
+          <t>L844: isolated marker/symbol line :: V</t>
         </is>
       </c>
       <c r="O78" s="1" t="inlineStr"/>
@@ -4255,16 +3979,12 @@
       <c r="H79" s="1" t="inlineStr"/>
       <c r="I79" s="1" t="inlineStr"/>
       <c r="J79" s="1" t="inlineStr"/>
-      <c r="K79" s="1" t="inlineStr">
-        <is>
-          <t>L912: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: youâ€”you could not help it. I will</t>
-        </is>
-      </c>
+      <c r="K79" s="1" t="inlineStr"/>
       <c r="L79" s="1" t="inlineStr"/>
       <c r="M79" s="1" t="inlineStr"/>
       <c r="N79" s="1" t="inlineStr">
         <is>
-          <t>L913: isolated marker/symbol line :: 350</t>
+          <t>L846: isolated marker/symbol line :: 55</t>
         </is>
       </c>
       <c r="O79" s="1" t="inlineStr"/>
@@ -4290,16 +4010,12 @@
       <c r="H80" s="1" t="inlineStr"/>
       <c r="I80" s="1" t="inlineStr"/>
       <c r="J80" s="1" t="inlineStr"/>
-      <c r="K80" s="1" t="inlineStr">
-        <is>
-          <t>L965: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: duties of Customs;â€� the duty, heret fore im-</t>
-        </is>
-      </c>
+      <c r="K80" s="1" t="inlineStr"/>
       <c r="L80" s="1" t="inlineStr"/>
       <c r="M80" s="1" t="inlineStr"/>
       <c r="N80" s="1" t="inlineStr">
         <is>
-          <t>L914: isolated marker/symbol line :: "</t>
+          <t>L848: isolated marker/symbol line :: 7</t>
         </is>
       </c>
       <c r="O80" s="1" t="inlineStr"/>
@@ -4325,16 +4041,12 @@
       <c r="H81" s="1" t="inlineStr"/>
       <c r="I81" s="1" t="inlineStr"/>
       <c r="J81" s="1" t="inlineStr"/>
-      <c r="K81" s="1" t="inlineStr">
-        <is>
-          <t>L1013: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER, U+02DC SMALL TILDE :: %â€œ Scottsâ€� Brand, Choiâ€˜e.</t>
-        </is>
-      </c>
+      <c r="K81" s="1" t="inlineStr"/>
       <c r="L81" s="1" t="inlineStr"/>
       <c r="M81" s="1" t="inlineStr"/>
       <c r="N81" s="1" t="inlineStr">
         <is>
-          <t>L915: isolated marker/symbol line :: "</t>
+          <t>L883: isolated marker/symbol line :: C</t>
         </is>
       </c>
       <c r="O81" s="1" t="inlineStr"/>
@@ -4360,16 +4072,12 @@
       <c r="H82" s="1" t="inlineStr"/>
       <c r="I82" s="1" t="inlineStr"/>
       <c r="J82" s="1" t="inlineStr"/>
-      <c r="K82" s="1" t="inlineStr">
-        <is>
-          <t>L1064: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: this night or morningâ€”hichever it</t>
-        </is>
-      </c>
+      <c r="K82" s="1" t="inlineStr"/>
       <c r="L82" s="1" t="inlineStr"/>
       <c r="M82" s="1" t="inlineStr"/>
       <c r="N82" s="1" t="inlineStr">
         <is>
-          <t>L916: isolated marker/symbol line :: d</t>
+          <t>L892: isolated marker/symbol line :: M</t>
         </is>
       </c>
       <c r="O82" s="1" t="inlineStr"/>
@@ -4395,16 +4103,12 @@
       <c r="H83" s="1" t="inlineStr"/>
       <c r="I83" s="1" t="inlineStr"/>
       <c r="J83" s="1" t="inlineStr"/>
-      <c r="K83" s="1" t="inlineStr">
-        <is>
-          <t>L1065: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œI It is past midnight, but not morn-</t>
-        </is>
-      </c>
+      <c r="K83" s="1" t="inlineStr"/>
       <c r="L83" s="1" t="inlineStr"/>
       <c r="M83" s="1" t="inlineStr"/>
       <c r="N83" s="1" t="inlineStr">
         <is>
-          <t>L919: isolated marker/symbol line :: 75</t>
+          <t>L905: symbol-only separator/garbage line :: 1960.</t>
         </is>
       </c>
       <c r="O83" s="1" t="inlineStr"/>
@@ -4430,16 +4134,12 @@
       <c r="H84" s="1" t="inlineStr"/>
       <c r="I84" s="1" t="inlineStr"/>
       <c r="J84" s="1" t="inlineStr"/>
-      <c r="K84" s="1" t="inlineStr">
-        <is>
-          <t>L1066: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: ofthe papers from the Reading Tables of the ing yet,â€� she replied ;" I always know</t>
-        </is>
-      </c>
+      <c r="K84" s="1" t="inlineStr"/>
       <c r="L84" s="1" t="inlineStr"/>
       <c r="M84" s="1" t="inlineStr"/>
       <c r="N84" s="1" t="inlineStr">
         <is>
-          <t>L920: isolated marker/symbol line :: 35</t>
+          <t>L909: symbol-only separator/garbage line :: 225 “0</t>
         </is>
       </c>
       <c r="O84" s="1" t="inlineStr"/>
@@ -4465,16 +4165,12 @@
       <c r="H85" s="1" t="inlineStr"/>
       <c r="I85" s="1" t="inlineStr"/>
       <c r="J85" s="1" t="inlineStr"/>
-      <c r="K85" s="1" t="inlineStr">
-        <is>
-          <t>L1070: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œ There is; but we should have to with her riding-master.</t>
-        </is>
-      </c>
+      <c r="K85" s="1" t="inlineStr"/>
       <c r="L85" s="1" t="inlineStr"/>
       <c r="M85" s="1" t="inlineStr"/>
       <c r="N85" s="1" t="inlineStr">
         <is>
-          <t>L923: isolated marker/symbol line :: 200</t>
+          <t>L913: isolated marker/symbol line :: 350</t>
         </is>
       </c>
       <c r="O85" s="1" t="inlineStr"/>
@@ -4500,16 +4196,12 @@
       <c r="H86" s="1" t="inlineStr"/>
       <c r="I86" s="1" t="inlineStr"/>
       <c r="J86" s="1" t="inlineStr"/>
-      <c r="K86" s="1" t="inlineStr">
-        <is>
-          <t>L1082: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€”ALSO,â€”</t>
-        </is>
-      </c>
+      <c r="K86" s="1" t="inlineStr"/>
       <c r="L86" s="1" t="inlineStr"/>
       <c r="M86" s="1" t="inlineStr"/>
       <c r="N86" s="1" t="inlineStr">
         <is>
-          <t>L924: isolated marker/symbol line :: 4</t>
+          <t>L914: isolated marker/symbol line :: "</t>
         </is>
       </c>
       <c r="O86" s="1" t="inlineStr"/>
@@ -4535,16 +4227,12 @@
       <c r="H87" s="1" t="inlineStr"/>
       <c r="I87" s="1" t="inlineStr"/>
       <c r="J87" s="1" t="inlineStr"/>
-      <c r="K87" s="1" t="inlineStr">
-        <is>
-          <t>L1106: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: CO.â€™</t>
-        </is>
-      </c>
+      <c r="K87" s="1" t="inlineStr"/>
       <c r="L87" s="1" t="inlineStr"/>
       <c r="M87" s="1" t="inlineStr"/>
       <c r="N87" s="1" t="inlineStr">
         <is>
-          <t>L925: isolated marker/symbol line :: X</t>
+          <t>L915: isolated marker/symbol line :: "</t>
         </is>
       </c>
       <c r="O87" s="1" t="inlineStr"/>
@@ -4570,16 +4258,12 @@
       <c r="H88" s="1" t="inlineStr"/>
       <c r="I88" s="1" t="inlineStr"/>
       <c r="J88" s="1" t="inlineStr"/>
-      <c r="K88" s="1" t="inlineStr">
-        <is>
-          <t>L1126: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | abbreviation/spacing may be garbled :: N.B.As the Messrs. Pannerâ€™s engage-</t>
-        </is>
-      </c>
+      <c r="K88" s="1" t="inlineStr"/>
       <c r="L88" s="1" t="inlineStr"/>
       <c r="M88" s="1" t="inlineStr"/>
       <c r="N88" s="1" t="inlineStr">
         <is>
-          <t>L931: isolated marker/symbol line :: 30</t>
+          <t>L916: isolated marker/symbol line :: d</t>
         </is>
       </c>
       <c r="O88" s="1" t="inlineStr"/>
@@ -4605,16 +4289,12 @@
       <c r="H89" s="1" t="inlineStr"/>
       <c r="I89" s="1" t="inlineStr"/>
       <c r="J89" s="1" t="inlineStr"/>
-      <c r="K89" s="1" t="inlineStr">
-        <is>
-          <t>L1136: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: â€”</t>
-        </is>
-      </c>
+      <c r="K89" s="1" t="inlineStr"/>
       <c r="L89" s="1" t="inlineStr"/>
       <c r="M89" s="1" t="inlineStr"/>
       <c r="N89" s="1" t="inlineStr">
         <is>
-          <t>L932: isolated marker/symbol line :: "</t>
+          <t>L919: isolated marker/symbol line :: 75</t>
         </is>
       </c>
       <c r="O89" s="1" t="inlineStr"/>
@@ -4640,16 +4320,12 @@
       <c r="H90" s="1" t="inlineStr"/>
       <c r="I90" s="1" t="inlineStr"/>
       <c r="J90" s="1" t="inlineStr"/>
-      <c r="K90" s="1" t="inlineStr">
-        <is>
-          <t>L1138: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: â€”</t>
-        </is>
-      </c>
+      <c r="K90" s="1" t="inlineStr"/>
       <c r="L90" s="1" t="inlineStr"/>
       <c r="M90" s="1" t="inlineStr"/>
       <c r="N90" s="1" t="inlineStr">
         <is>
-          <t>L933: isolated marker/symbol line :: -</t>
+          <t>L920: isolated marker/symbol line :: 35</t>
         </is>
       </c>
       <c r="O90" s="1" t="inlineStr"/>
@@ -4675,16 +4351,12 @@
       <c r="H91" s="1" t="inlineStr"/>
       <c r="I91" s="1" t="inlineStr"/>
       <c r="J91" s="1" t="inlineStr"/>
-      <c r="K91" s="1" t="inlineStr">
-        <is>
-          <t>L1156: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
+      <c r="K91" s="1" t="inlineStr"/>
       <c r="L91" s="1" t="inlineStr"/>
       <c r="M91" s="1" t="inlineStr"/>
       <c r="N91" s="1" t="inlineStr">
         <is>
-          <t>L937: isolated marker/symbol line :: 27</t>
+          <t>L923: isolated marker/symbol line :: 200</t>
         </is>
       </c>
       <c r="O91" s="1" t="inlineStr"/>
@@ -4715,7 +4387,7 @@
       <c r="M92" s="1" t="inlineStr"/>
       <c r="N92" s="1" t="inlineStr">
         <is>
-          <t>L938: isolated marker/symbol line :: 68</t>
+          <t>L924: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O92" s="1" t="inlineStr"/>
@@ -4746,7 +4418,7 @@
       <c r="M93" s="1" t="inlineStr"/>
       <c r="N93" s="1" t="inlineStr">
         <is>
-          <t>L939: isolated marker/symbol line :: 14</t>
+          <t>L925: isolated marker/symbol line :: X</t>
         </is>
       </c>
       <c r="O93" s="1" t="inlineStr"/>
@@ -4777,7 +4449,7 @@
       <c r="M94" s="1" t="inlineStr"/>
       <c r="N94" s="1" t="inlineStr">
         <is>
-          <t>L949: isolated marker/symbol line :: e</t>
+          <t>L931: isolated marker/symbol line :: 30</t>
         </is>
       </c>
       <c r="O94" s="1" t="inlineStr"/>
@@ -4808,7 +4480,7 @@
       <c r="M95" s="1" t="inlineStr"/>
       <c r="N95" s="1" t="inlineStr">
         <is>
-          <t>L950: isolated marker/symbol line :: n</t>
+          <t>L932: isolated marker/symbol line :: "</t>
         </is>
       </c>
       <c r="O95" s="1" t="inlineStr"/>
@@ -4839,7 +4511,7 @@
       <c r="M96" s="1" t="inlineStr"/>
       <c r="N96" s="1" t="inlineStr">
         <is>
-          <t>L951: isolated marker/symbol line :: B</t>
+          <t>L933: isolated marker/symbol line :: -</t>
         </is>
       </c>
       <c r="O96" s="1" t="inlineStr"/>
@@ -4870,7 +4542,7 @@
       <c r="M97" s="1" t="inlineStr"/>
       <c r="N97" s="1" t="inlineStr">
         <is>
-          <t>L961: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L935: stray/suspicious non-ASCII glyph(s): U+6C99 CJK UNIFIED IDEOGRAPH-6C99 | isolated marker/symbol line :: 沙</t>
         </is>
       </c>
       <c r="O97" s="1" t="inlineStr"/>
@@ -4901,7 +4573,7 @@
       <c r="M98" s="1" t="inlineStr"/>
       <c r="N98" s="1" t="inlineStr">
         <is>
-          <t>L994: isolated marker/symbol line :: 2</t>
+          <t>L936: stray/suspicious non-ASCII glyph(s): U+5C81 CJK UNIFIED IDEOGRAPH-5C81 | isolated marker/symbol line :: 岁</t>
         </is>
       </c>
       <c r="O98" s="1" t="inlineStr"/>
@@ -4932,7 +4604,7 @@
       <c r="M99" s="1" t="inlineStr"/>
       <c r="N99" s="1" t="inlineStr">
         <is>
-          <t>L1081: isolated marker/symbol line :: '</t>
+          <t>L937: isolated marker/symbol line :: 27</t>
         </is>
       </c>
       <c r="O99" s="1" t="inlineStr"/>
@@ -4963,7 +4635,7 @@
       <c r="M100" s="1" t="inlineStr"/>
       <c r="N100" s="1" t="inlineStr">
         <is>
-          <t>L1093: isolated marker/symbol line :: 2</t>
+          <t>L938: isolated marker/symbol line :: 68</t>
         </is>
       </c>
       <c r="O100" s="1" t="inlineStr"/>
@@ -4994,7 +4666,7 @@
       <c r="M101" s="1" t="inlineStr"/>
       <c r="N101" s="1" t="inlineStr">
         <is>
-          <t>L1098: isolated marker/symbol line :: "</t>
+          <t>L939: isolated marker/symbol line :: 14</t>
         </is>
       </c>
       <c r="O101" s="1" t="inlineStr"/>
@@ -5025,7 +4697,7 @@
       <c r="M102" s="1" t="inlineStr"/>
       <c r="N102" s="1" t="inlineStr">
         <is>
-          <t>L1126: isolated marker/symbol line :: ç—…</t>
+          <t>L947: stray/suspicious non-ASCII glyph(s): U+5FC3 CJK UNIFIED IDEOGRAPH-5FC3 | isolated marker/symbol line :: 心</t>
         </is>
       </c>
       <c r="O102" s="1" t="inlineStr"/>
@@ -5056,7 +4728,7 @@
       <c r="M103" s="1" t="inlineStr"/>
       <c r="N103" s="1" t="inlineStr">
         <is>
-          <t>L1140: isolated marker/symbol line :: 0</t>
+          <t>L948: stray/suspicious non-ASCII glyph(s): U+5FC3 CJK UNIFIED IDEOGRAPH-5FC3 | isolated marker/symbol line :: 心</t>
         </is>
       </c>
       <c r="O103" s="1" t="inlineStr"/>
@@ -5071,6 +4743,316 @@
       <c r="X103" s="1" t="inlineStr"/>
       <c r="Y103" s="1" t="inlineStr"/>
     </row>
+    <row r="104">
+      <c r="A104" s="1" t="inlineStr"/>
+      <c r="B104" s="1" t="inlineStr"/>
+      <c r="C104" s="1" t="inlineStr"/>
+      <c r="D104" s="1" t="inlineStr"/>
+      <c r="E104" s="1" t="inlineStr"/>
+      <c r="F104" s="1" t="inlineStr"/>
+      <c r="G104" s="1" t="inlineStr"/>
+      <c r="H104" s="1" t="inlineStr"/>
+      <c r="I104" s="1" t="inlineStr"/>
+      <c r="J104" s="1" t="inlineStr"/>
+      <c r="K104" s="1" t="inlineStr"/>
+      <c r="L104" s="1" t="inlineStr"/>
+      <c r="M104" s="1" t="inlineStr"/>
+      <c r="N104" s="1" t="inlineStr">
+        <is>
+          <t>L949: isolated marker/symbol line :: e</t>
+        </is>
+      </c>
+      <c r="O104" s="1" t="inlineStr"/>
+      <c r="P104" s="1" t="inlineStr"/>
+      <c r="Q104" s="1" t="inlineStr"/>
+      <c r="R104" s="1" t="inlineStr"/>
+      <c r="S104" s="1" t="inlineStr"/>
+      <c r="T104" s="1" t="inlineStr"/>
+      <c r="U104" s="1" t="inlineStr"/>
+      <c r="V104" s="1" t="inlineStr"/>
+      <c r="W104" s="1" t="inlineStr"/>
+      <c r="X104" s="1" t="inlineStr"/>
+      <c r="Y104" s="1" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="1" t="inlineStr"/>
+      <c r="B105" s="1" t="inlineStr"/>
+      <c r="C105" s="1" t="inlineStr"/>
+      <c r="D105" s="1" t="inlineStr"/>
+      <c r="E105" s="1" t="inlineStr"/>
+      <c r="F105" s="1" t="inlineStr"/>
+      <c r="G105" s="1" t="inlineStr"/>
+      <c r="H105" s="1" t="inlineStr"/>
+      <c r="I105" s="1" t="inlineStr"/>
+      <c r="J105" s="1" t="inlineStr"/>
+      <c r="K105" s="1" t="inlineStr"/>
+      <c r="L105" s="1" t="inlineStr"/>
+      <c r="M105" s="1" t="inlineStr"/>
+      <c r="N105" s="1" t="inlineStr">
+        <is>
+          <t>L950: isolated marker/symbol line :: n</t>
+        </is>
+      </c>
+      <c r="O105" s="1" t="inlineStr"/>
+      <c r="P105" s="1" t="inlineStr"/>
+      <c r="Q105" s="1" t="inlineStr"/>
+      <c r="R105" s="1" t="inlineStr"/>
+      <c r="S105" s="1" t="inlineStr"/>
+      <c r="T105" s="1" t="inlineStr"/>
+      <c r="U105" s="1" t="inlineStr"/>
+      <c r="V105" s="1" t="inlineStr"/>
+      <c r="W105" s="1" t="inlineStr"/>
+      <c r="X105" s="1" t="inlineStr"/>
+      <c r="Y105" s="1" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="1" t="inlineStr"/>
+      <c r="B106" s="1" t="inlineStr"/>
+      <c r="C106" s="1" t="inlineStr"/>
+      <c r="D106" s="1" t="inlineStr"/>
+      <c r="E106" s="1" t="inlineStr"/>
+      <c r="F106" s="1" t="inlineStr"/>
+      <c r="G106" s="1" t="inlineStr"/>
+      <c r="H106" s="1" t="inlineStr"/>
+      <c r="I106" s="1" t="inlineStr"/>
+      <c r="J106" s="1" t="inlineStr"/>
+      <c r="K106" s="1" t="inlineStr"/>
+      <c r="L106" s="1" t="inlineStr"/>
+      <c r="M106" s="1" t="inlineStr"/>
+      <c r="N106" s="1" t="inlineStr">
+        <is>
+          <t>L951: isolated marker/symbol line :: B</t>
+        </is>
+      </c>
+      <c r="O106" s="1" t="inlineStr"/>
+      <c r="P106" s="1" t="inlineStr"/>
+      <c r="Q106" s="1" t="inlineStr"/>
+      <c r="R106" s="1" t="inlineStr"/>
+      <c r="S106" s="1" t="inlineStr"/>
+      <c r="T106" s="1" t="inlineStr"/>
+      <c r="U106" s="1" t="inlineStr"/>
+      <c r="V106" s="1" t="inlineStr"/>
+      <c r="W106" s="1" t="inlineStr"/>
+      <c r="X106" s="1" t="inlineStr"/>
+      <c r="Y106" s="1" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="1" t="inlineStr"/>
+      <c r="B107" s="1" t="inlineStr"/>
+      <c r="C107" s="1" t="inlineStr"/>
+      <c r="D107" s="1" t="inlineStr"/>
+      <c r="E107" s="1" t="inlineStr"/>
+      <c r="F107" s="1" t="inlineStr"/>
+      <c r="G107" s="1" t="inlineStr"/>
+      <c r="H107" s="1" t="inlineStr"/>
+      <c r="I107" s="1" t="inlineStr"/>
+      <c r="J107" s="1" t="inlineStr"/>
+      <c r="K107" s="1" t="inlineStr"/>
+      <c r="L107" s="1" t="inlineStr"/>
+      <c r="M107" s="1" t="inlineStr"/>
+      <c r="N107" s="1" t="inlineStr">
+        <is>
+          <t>L961: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
+        </is>
+      </c>
+      <c r="O107" s="1" t="inlineStr"/>
+      <c r="P107" s="1" t="inlineStr"/>
+      <c r="Q107" s="1" t="inlineStr"/>
+      <c r="R107" s="1" t="inlineStr"/>
+      <c r="S107" s="1" t="inlineStr"/>
+      <c r="T107" s="1" t="inlineStr"/>
+      <c r="U107" s="1" t="inlineStr"/>
+      <c r="V107" s="1" t="inlineStr"/>
+      <c r="W107" s="1" t="inlineStr"/>
+      <c r="X107" s="1" t="inlineStr"/>
+      <c r="Y107" s="1" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="1" t="inlineStr"/>
+      <c r="B108" s="1" t="inlineStr"/>
+      <c r="C108" s="1" t="inlineStr"/>
+      <c r="D108" s="1" t="inlineStr"/>
+      <c r="E108" s="1" t="inlineStr"/>
+      <c r="F108" s="1" t="inlineStr"/>
+      <c r="G108" s="1" t="inlineStr"/>
+      <c r="H108" s="1" t="inlineStr"/>
+      <c r="I108" s="1" t="inlineStr"/>
+      <c r="J108" s="1" t="inlineStr"/>
+      <c r="K108" s="1" t="inlineStr"/>
+      <c r="L108" s="1" t="inlineStr"/>
+      <c r="M108" s="1" t="inlineStr"/>
+      <c r="N108" s="1" t="inlineStr">
+        <is>
+          <t>L994: isolated marker/symbol line :: 2</t>
+        </is>
+      </c>
+      <c r="O108" s="1" t="inlineStr"/>
+      <c r="P108" s="1" t="inlineStr"/>
+      <c r="Q108" s="1" t="inlineStr"/>
+      <c r="R108" s="1" t="inlineStr"/>
+      <c r="S108" s="1" t="inlineStr"/>
+      <c r="T108" s="1" t="inlineStr"/>
+      <c r="U108" s="1" t="inlineStr"/>
+      <c r="V108" s="1" t="inlineStr"/>
+      <c r="W108" s="1" t="inlineStr"/>
+      <c r="X108" s="1" t="inlineStr"/>
+      <c r="Y108" s="1" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="1" t="inlineStr"/>
+      <c r="B109" s="1" t="inlineStr"/>
+      <c r="C109" s="1" t="inlineStr"/>
+      <c r="D109" s="1" t="inlineStr"/>
+      <c r="E109" s="1" t="inlineStr"/>
+      <c r="F109" s="1" t="inlineStr"/>
+      <c r="G109" s="1" t="inlineStr"/>
+      <c r="H109" s="1" t="inlineStr"/>
+      <c r="I109" s="1" t="inlineStr"/>
+      <c r="J109" s="1" t="inlineStr"/>
+      <c r="K109" s="1" t="inlineStr"/>
+      <c r="L109" s="1" t="inlineStr"/>
+      <c r="M109" s="1" t="inlineStr"/>
+      <c r="N109" s="1" t="inlineStr">
+        <is>
+          <t>L1081: isolated marker/symbol line :: '</t>
+        </is>
+      </c>
+      <c r="O109" s="1" t="inlineStr"/>
+      <c r="P109" s="1" t="inlineStr"/>
+      <c r="Q109" s="1" t="inlineStr"/>
+      <c r="R109" s="1" t="inlineStr"/>
+      <c r="S109" s="1" t="inlineStr"/>
+      <c r="T109" s="1" t="inlineStr"/>
+      <c r="U109" s="1" t="inlineStr"/>
+      <c r="V109" s="1" t="inlineStr"/>
+      <c r="W109" s="1" t="inlineStr"/>
+      <c r="X109" s="1" t="inlineStr"/>
+      <c r="Y109" s="1" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="1" t="inlineStr"/>
+      <c r="B110" s="1" t="inlineStr"/>
+      <c r="C110" s="1" t="inlineStr"/>
+      <c r="D110" s="1" t="inlineStr"/>
+      <c r="E110" s="1" t="inlineStr"/>
+      <c r="F110" s="1" t="inlineStr"/>
+      <c r="G110" s="1" t="inlineStr"/>
+      <c r="H110" s="1" t="inlineStr"/>
+      <c r="I110" s="1" t="inlineStr"/>
+      <c r="J110" s="1" t="inlineStr"/>
+      <c r="K110" s="1" t="inlineStr"/>
+      <c r="L110" s="1" t="inlineStr"/>
+      <c r="M110" s="1" t="inlineStr"/>
+      <c r="N110" s="1" t="inlineStr">
+        <is>
+          <t>L1093: isolated marker/symbol line :: 2</t>
+        </is>
+      </c>
+      <c r="O110" s="1" t="inlineStr"/>
+      <c r="P110" s="1" t="inlineStr"/>
+      <c r="Q110" s="1" t="inlineStr"/>
+      <c r="R110" s="1" t="inlineStr"/>
+      <c r="S110" s="1" t="inlineStr"/>
+      <c r="T110" s="1" t="inlineStr"/>
+      <c r="U110" s="1" t="inlineStr"/>
+      <c r="V110" s="1" t="inlineStr"/>
+      <c r="W110" s="1" t="inlineStr"/>
+      <c r="X110" s="1" t="inlineStr"/>
+      <c r="Y110" s="1" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="1" t="inlineStr"/>
+      <c r="B111" s="1" t="inlineStr"/>
+      <c r="C111" s="1" t="inlineStr"/>
+      <c r="D111" s="1" t="inlineStr"/>
+      <c r="E111" s="1" t="inlineStr"/>
+      <c r="F111" s="1" t="inlineStr"/>
+      <c r="G111" s="1" t="inlineStr"/>
+      <c r="H111" s="1" t="inlineStr"/>
+      <c r="I111" s="1" t="inlineStr"/>
+      <c r="J111" s="1" t="inlineStr"/>
+      <c r="K111" s="1" t="inlineStr"/>
+      <c r="L111" s="1" t="inlineStr"/>
+      <c r="M111" s="1" t="inlineStr"/>
+      <c r="N111" s="1" t="inlineStr">
+        <is>
+          <t>L1098: isolated marker/symbol line :: "</t>
+        </is>
+      </c>
+      <c r="O111" s="1" t="inlineStr"/>
+      <c r="P111" s="1" t="inlineStr"/>
+      <c r="Q111" s="1" t="inlineStr"/>
+      <c r="R111" s="1" t="inlineStr"/>
+      <c r="S111" s="1" t="inlineStr"/>
+      <c r="T111" s="1" t="inlineStr"/>
+      <c r="U111" s="1" t="inlineStr"/>
+      <c r="V111" s="1" t="inlineStr"/>
+      <c r="W111" s="1" t="inlineStr"/>
+      <c r="X111" s="1" t="inlineStr"/>
+      <c r="Y111" s="1" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="1" t="inlineStr"/>
+      <c r="B112" s="1" t="inlineStr"/>
+      <c r="C112" s="1" t="inlineStr"/>
+      <c r="D112" s="1" t="inlineStr"/>
+      <c r="E112" s="1" t="inlineStr"/>
+      <c r="F112" s="1" t="inlineStr"/>
+      <c r="G112" s="1" t="inlineStr"/>
+      <c r="H112" s="1" t="inlineStr"/>
+      <c r="I112" s="1" t="inlineStr"/>
+      <c r="J112" s="1" t="inlineStr"/>
+      <c r="K112" s="1" t="inlineStr"/>
+      <c r="L112" s="1" t="inlineStr"/>
+      <c r="M112" s="1" t="inlineStr"/>
+      <c r="N112" s="1" t="inlineStr">
+        <is>
+          <t>L1126: stray/suspicious non-ASCII glyph(s): U+75C5 CJK UNIFIED IDEOGRAPH-75C5 | isolated marker/symbol line :: 病</t>
+        </is>
+      </c>
+      <c r="O112" s="1" t="inlineStr"/>
+      <c r="P112" s="1" t="inlineStr"/>
+      <c r="Q112" s="1" t="inlineStr"/>
+      <c r="R112" s="1" t="inlineStr"/>
+      <c r="S112" s="1" t="inlineStr"/>
+      <c r="T112" s="1" t="inlineStr"/>
+      <c r="U112" s="1" t="inlineStr"/>
+      <c r="V112" s="1" t="inlineStr"/>
+      <c r="W112" s="1" t="inlineStr"/>
+      <c r="X112" s="1" t="inlineStr"/>
+      <c r="Y112" s="1" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="1" t="inlineStr"/>
+      <c r="B113" s="1" t="inlineStr"/>
+      <c r="C113" s="1" t="inlineStr"/>
+      <c r="D113" s="1" t="inlineStr"/>
+      <c r="E113" s="1" t="inlineStr"/>
+      <c r="F113" s="1" t="inlineStr"/>
+      <c r="G113" s="1" t="inlineStr"/>
+      <c r="H113" s="1" t="inlineStr"/>
+      <c r="I113" s="1" t="inlineStr"/>
+      <c r="J113" s="1" t="inlineStr"/>
+      <c r="K113" s="1" t="inlineStr"/>
+      <c r="L113" s="1" t="inlineStr"/>
+      <c r="M113" s="1" t="inlineStr"/>
+      <c r="N113" s="1" t="inlineStr">
+        <is>
+          <t>L1140: isolated marker/symbol line :: 0</t>
+        </is>
+      </c>
+      <c r="O113" s="1" t="inlineStr"/>
+      <c r="P113" s="1" t="inlineStr"/>
+      <c r="Q113" s="1" t="inlineStr"/>
+      <c r="R113" s="1" t="inlineStr"/>
+      <c r="S113" s="1" t="inlineStr"/>
+      <c r="T113" s="1" t="inlineStr"/>
+      <c r="U113" s="1" t="inlineStr"/>
+      <c r="V113" s="1" t="inlineStr"/>
+      <c r="W113" s="1" t="inlineStr"/>
+      <c r="X113" s="1" t="inlineStr"/>
+      <c r="Y113" s="1" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
